--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,110 +531,438 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,92 +531,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>331.57222</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>39.22</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.1575</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>L19066036</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,28 +635,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>20.70997</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UEFA Super Cup</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -690,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +739,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -762,47 +754,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786310047</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>206.726644</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,110 +851,550 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>65.17485</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1786309443</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>87.48302</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,12 +542,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,12 +646,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,92 +739,84 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>331.57222</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>74.68</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1.3613</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>L19066036</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,92 +843,84 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>20.70997</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>65.17485</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1.745</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>L19066036</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -978,22 +962,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1018,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786310047</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>206.726644</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,36 +1059,44 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>65.17485</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -1122,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786309443</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>87.48302</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1171,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1194,47 +1186,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.1575</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786294983</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>249.015873</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,110 +1283,326 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,7 +654,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,12 +758,12 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,12 +862,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -920,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,92 +955,84 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20.70997</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>74.68</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1.3613</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>L19066036</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,12 +1059,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786310047</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>206.726644</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1186,22 +1186,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>65.17485</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786309443</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>87.48302</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1291,28 +1291,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.1575</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -1330,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1360,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786294983</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>249.015873</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1395,81 +1403,73 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>72.13</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1.2112</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>L19066036</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>1786294922</t>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>374.69216</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,110 +1499,222 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,32 +561,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786371203</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>22.812785</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,23 +643,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -667,7 +671,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -758,7 +766,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -824,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,12 +870,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -928,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,12 +974,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1032,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,39 +1067,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>20.70997</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1186,22 +1186,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786310047</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>206.726644</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,12 +1283,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>65.17485</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786309443</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>87.48302</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1403,28 +1403,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.1575</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -1442,7 +1450,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786294983</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>249.015873</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1507,54 +1515,46 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>105.38217</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.2812</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>374.69216</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,110 +1611,222 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,39 +546,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>13.13154</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786390904</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>202.023692</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,47 +658,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11.30985</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786390902</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>173.997692</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,23 +755,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -779,7 +783,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -802,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786371203</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>22.812785</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,23 +867,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -883,7 +895,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -936,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -974,12 +990,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1040,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1078,12 +1094,12 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1144,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,39 +1187,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1226,7 +1234,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,39 +1291,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>20.70997</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786310047</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>206.726644</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,36 +1507,44 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>65.17485</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -1554,7 +1562,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786309443</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>87.48302</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1619,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1626,47 +1634,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.1575</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1696,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786294983</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>249.015873</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,110 +1731,326 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>216.99999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786409895</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>443.989749</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,7 +650,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>13.13154</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786390904</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>202.023692</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,39 +762,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>11.30985</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -810,7 +802,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786390902</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>173.997692</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,12 +874,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -897,32 +889,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786371203</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>22.812785</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,23 +971,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1003,7 +999,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1083,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1198,12 +1198,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1302,12 +1302,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,39 +1395,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>20.70997</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1450,7 +1442,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,12 +1499,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1522,22 +1514,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1562,7 +1554,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786310047</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>206.726644</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1611,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,22 +1626,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>65.17485</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1674,7 +1666,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1704,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786309443</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>87.48302</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,7 +1723,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1739,28 +1731,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.1575</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786294983</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>249.015873</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1843,54 +1843,46 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>105.38217</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.2812</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1930,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>374.69216</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,110 +1939,222 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,12 +542,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786421953</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>2.040816</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,39 +635,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -690,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786421917</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>138.77551</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,39 +739,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -802,7 +786,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +816,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786421886</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +826,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>18.414322</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,54 +843,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>216.99999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -914,7 +890,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +920,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786409895</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +930,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>443.989749</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +947,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,47 +962,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13.13154</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786390904</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>202.023692</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,31 +1059,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>11.30985</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1130,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786390902</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>173.997692</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,23 +1171,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1211,7 +1199,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1234,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786371203</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>22.812785</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,23 +1283,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1315,7 +1311,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1406,12 +1406,12 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,39 +1499,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1554,7 +1546,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1576,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1586,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,39 +1603,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1666,7 +1650,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1696,7 +1680,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1690,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,39 +1707,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>20.70997</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1778,7 +1754,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1784,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1794,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,7 +1811,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1843,28 +1819,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -1882,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786310047</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>206.726644</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,12 +1923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1954,47 +1938,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>65.17485</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2024,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786309443</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2034,7 +2018,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>87.48302</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,110 +2035,438 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.00999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786421953</t>
+          <t>1786424623</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.040816</t>
+          <t>10.977151</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,7 +654,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786421917</t>
+          <t>1786421953</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>138.77551</t>
+          <t>2.040816</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -750,12 +758,12 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786421886</t>
+          <t>1786421917</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>18.414322</t>
+          <t>138.77551</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,7 +862,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -920,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786421886</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>18.414322</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,39 +955,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>216.99999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786409895</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>443.989749</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>13.13154</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786390904</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>202.023692</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,12 +1171,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1186,39 +1186,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>11.30985</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786390902</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>173.997692</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,12 +1283,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1313,32 +1313,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786371203</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>22.812785</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,23 +1395,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1419,7 +1423,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1472,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1510,7 +1518,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1576,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1586,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1614,12 +1622,12 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1680,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,7 +1715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1718,12 +1726,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1784,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1794,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,39 +1819,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>20.70997</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,12 +1923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1938,22 +1938,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786310047</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>206.726644</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,12 +2035,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2050,22 +2050,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>65.17485</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786309443</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>87.48302</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2155,28 +2155,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.1575</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -2194,7 +2202,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2224,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786294983</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>249.015873</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,7 +2259,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2259,54 +2267,46 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>105.38217</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.2812</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>374.69216</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,110 +2363,222 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,54 +531,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.00999</t>
+          <t>312.25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.4825</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786424623</t>
+          <t>1786431942</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>10.977151</t>
+          <t>647.150259</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +635,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.00999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -690,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786421953</t>
+          <t>1786424623</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.040816</t>
+          <t>10.977151</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786421917</t>
+          <t>1786421953</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>138.77551</t>
+          <t>2.040816</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,12 +862,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786421886</t>
+          <t>1786421917</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>18.414322</t>
+          <t>138.77551</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,7 +966,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786421886</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>18.414322</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,39 +1059,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>216.99999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1114,7 +1106,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786409895</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>443.989749</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1186,7 +1178,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>13.13154</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1256,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786390904</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>202.023692</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,12 +1275,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1298,39 +1290,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>11.30985</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -1338,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786390902</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>173.997692</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,12 +1387,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1410,12 +1402,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1425,32 +1417,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786371203</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>22.812785</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,23 +1499,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1531,7 +1527,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1622,7 +1622,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,7 +1715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1726,12 +1726,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1830,12 +1830,12 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,39 +1923,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>20.70997</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1978,7 +1970,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2008,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2018,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,12 +2027,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2050,22 +2042,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2090,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2120,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786310047</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2130,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>206.726644</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,12 +2139,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2162,22 +2154,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>65.17485</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 1.5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2202,7 +2194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2232,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786309443</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2242,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>87.48302</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,7 +2251,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2267,28 +2259,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.1575</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786294983</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>249.015873</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2371,54 +2371,46 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>105.38217</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.2812</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2458,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>374.69216</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,110 +2467,222 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
+          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>312.25</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786431942</t>
+          <t>1786462484</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>647.150259</t>
+          <t>24.911111</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,12 +650,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.00999</t>
+          <t>23.9188</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -665,24 +665,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -690,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786424623</t>
+          <t>1786460921</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>10.977151</t>
+          <t>111.250233</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,28 +747,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -794,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786421953</t>
+          <t>1786459823</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.040816</t>
+          <t>3.232323</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +851,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786421917</t>
+          <t>1786459704</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>138.77551</t>
+          <t>343.089431</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,28 +955,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>280.99999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786421886</t>
+          <t>1786459347</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18.414322</t>
+          <t>456.910553</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,23 +1059,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>312.25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.4825</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786431942</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>647.150259</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,12 +1163,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1178,22 +1178,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>6.00999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786424623</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>10.977151</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,39 +1275,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1330,7 +1322,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1360,7 +1352,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786421953</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1370,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>2.040816</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,54 +1379,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -1442,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786421917</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>138.77551</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,62 +1483,54 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1560,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786421886</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1570,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>18.414322</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,28 +1587,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>216.99999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1658,7 +1634,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1688,7 +1664,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786409895</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1674,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>443.989749</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,31 +1691,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>13.13154</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1762,7 +1746,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1792,7 +1776,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786390904</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1786,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>202.023692</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,31 +1803,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>11.30985</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1866,7 +1858,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1888,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786390902</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1898,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>173.997692</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,23 +1915,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1947,7 +1943,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786371203</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>22.812785</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2042,22 +2042,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,39 +2139,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2194,7 +2186,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2224,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2226,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,39 +2243,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2306,7 +2290,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2336,7 +2320,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2346,7 +2330,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,28 +2347,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UEFA Super Cup</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2410,7 +2394,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2440,7 +2424,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2450,7 +2434,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,27 +2451,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>20.70997</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2495,31 +2475,27 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
@@ -2552,7 +2528,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2562,7 +2538,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,110 +2555,662 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>74.68</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1786310047</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>206.726644</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>65.17485</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1786309443</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>87.48302</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
+          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786462484</t>
+          <t>1786466862</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>24.911111</t>
+          <t>586.482759</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,62 +635,54 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
+          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23.9188</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786460921</t>
+          <t>1786466015</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>111.250233</t>
+          <t>16.675105</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,31 +739,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
+          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>119.23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -794,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786459823</t>
+          <t>1786465613</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.232323</t>
+          <t>662.388889</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +851,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
+          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -898,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786459704</t>
+          <t>1786462484</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>343.089431</t>
+          <t>24.911111</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,31 +955,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
+          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>280.99999</t>
+          <t>23.9188</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1002,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786459347</t>
+          <t>1786460921</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>456.910553</t>
+          <t>111.250233</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,28 +1067,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
+          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>312.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1106,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1136,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786431942</t>
+          <t>1786459823</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>647.150259</t>
+          <t>3.232323</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,54 +1171,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6.00999</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786424623</t>
+          <t>1786459704</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>10.977151</t>
+          <t>343.089431</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,28 +1275,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>280.99999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786421953</t>
+          <t>1786459347</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.040816</t>
+          <t>456.910553</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,23 +1379,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>312.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.4825</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786421917</t>
+          <t>1786431942</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>138.77551</t>
+          <t>647.150259</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,31 +1483,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6.00999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1530,7 +1538,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1560,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786421886</t>
+          <t>1786424623</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>18.414322</t>
+          <t>10.977151</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1598,12 +1606,12 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1664,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786421953</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1674,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>2.040816</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,39 +1699,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786421917</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>138.77551</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,39 +1803,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1858,7 +1850,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1888,7 +1880,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786421886</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1890,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>18.414322</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,54 +1907,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>216.99999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -1970,7 +1954,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2000,7 +1984,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786409895</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2010,7 +1994,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>443.989749</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,12 +2011,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2042,47 +2026,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13.13154</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2112,7 +2096,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786390904</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2106,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>202.023692</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,31 +2123,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>11.30985</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2186,7 +2178,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2216,7 +2208,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786390902</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2226,7 +2218,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>173.997692</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,23 +2235,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2267,7 +2263,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786371203</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>22.812785</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,23 +2347,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2371,7 +2375,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2424,7 +2432,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2434,7 +2442,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2451,7 +2459,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2462,12 +2470,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2528,7 +2536,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2538,7 +2546,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,39 +2563,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,39 +2667,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2722,7 +2714,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2752,7 +2744,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2762,7 +2754,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,39 +2771,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>20.70997</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2834,7 +2818,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2864,7 +2848,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2874,7 +2858,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,7 +2875,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2899,28 +2883,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.3613</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -2938,7 +2930,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2968,7 +2960,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786310047</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2978,7 +2970,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>206.726644</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,12 +2987,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3010,47 +3002,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>65.17485</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.745</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3080,7 +3072,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786309443</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3090,7 +3082,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>87.48302</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,110 +3099,438 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V29"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
+          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,23 +539,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786466862</t>
+          <t>1786477844</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>586.482759</t>
+          <t>44.882051</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,28 +643,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
+          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786466015</t>
+          <t>1786477225</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>16.675105</t>
+          <t>6016.713092</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,39 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
+          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>119.23</t>
+          <t>688.37615</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -794,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786465613</t>
+          <t>1786476767</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>662.388889</t>
+          <t>1533.98585</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
+          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -859,15 +859,19 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -875,7 +879,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -898,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786462484</t>
+          <t>1786476263</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>24.911111</t>
+          <t>73.723077</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,12 +963,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
+          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -970,47 +978,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.9188</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.3075</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786460921</t>
+          <t>1786473059</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>111.250233</t>
+          <t>15.447154</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,28 +1075,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
+          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1114,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786459823</t>
+          <t>1786466862</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3.232323</t>
+          <t>586.482759</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,28 +1179,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
+          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1218,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786459704</t>
+          <t>1786466015</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>343.089431</t>
+          <t>16.675105</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,31 +1283,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
+          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>280.99999</t>
+          <t>119.23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1322,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1352,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786459347</t>
+          <t>1786465613</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>456.910553</t>
+          <t>662.388889</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
+          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1390,17 +1406,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>312.25</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1426,7 +1442,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1456,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786431942</t>
+          <t>1786462484</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>647.150259</t>
+          <t>24.911111</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,12 +1499,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1498,12 +1514,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.00999</t>
+          <t>23.9188</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1513,24 +1529,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -1538,7 +1554,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1568,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786424623</t>
+          <t>1786460921</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1578,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>10.977151</t>
+          <t>111.250233</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,28 +1611,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1642,7 +1658,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1672,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786421953</t>
+          <t>1786459823</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1682,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2.040816</t>
+          <t>3.232323</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,28 +1715,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1746,7 +1762,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1776,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786421917</t>
+          <t>1786459704</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1786,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>138.77551</t>
+          <t>343.089431</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,28 +1819,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>280.99999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1850,7 +1866,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1880,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786421886</t>
+          <t>1786459347</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1890,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>18.414322</t>
+          <t>456.910553</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1907,23 +1923,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>312.25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.4825</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1984,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786431942</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1994,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>647.150259</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,12 +2027,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2026,22 +2042,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>6.00999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2066,7 +2082,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2096,7 +2112,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786424623</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2106,7 +2122,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>10.977151</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,39 +2139,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2178,7 +2186,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2208,7 +2216,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786421953</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2218,7 +2226,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>2.040816</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,54 +2243,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786421917</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>138.77551</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,62 +2347,54 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2432,7 +2424,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786421886</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2442,7 +2434,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>18.414322</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,28 +2451,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>216.99999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2506,7 +2498,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2536,7 +2528,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786409895</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2546,7 +2538,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>443.989749</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,31 +2555,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>13.13154</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786390904</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>202.023692</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,31 +2667,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>11.30985</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2714,7 +2722,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2744,7 +2752,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786390902</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2754,7 +2762,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>173.997692</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,23 +2779,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2795,7 +2807,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2818,7 +2834,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2848,7 +2864,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786371203</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2858,7 +2874,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>22.812785</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2875,12 +2891,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2890,22 +2906,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2930,7 +2946,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2960,7 +2976,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2970,7 +2986,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,39 +3003,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3042,7 +3050,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3072,7 +3080,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3082,7 +3090,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3099,39 +3107,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,28 +3211,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UEFA Super Cup</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3315,27 +3315,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>20.70997</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.7963</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3343,31 +3339,27 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
@@ -3400,7 +3392,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786316213</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3410,7 +3402,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>26.009381</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3427,110 +3419,662 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>74.68</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1786310047</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>206.726644</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>65.17485</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1786309443</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>87.48302</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
+          <t>0x5e9b92a3ee864ed306ae19b1eb8415371da432df1801adf9df4096158c2ada97</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>22.15226</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786477844</t>
+          <t>1786491019</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>44.882051</t>
+          <t>49.502257</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +635,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
+          <t>0x23733dbdf9fa3729981e360673c4b7d7c10ff2531e371c5badad3796d6c9c512</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>27.55999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -690,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786477225</t>
+          <t>1786490560</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6016.713092</t>
+          <t>49.43496</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,23 +747,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
+          <t>0x0727088f0a4a30c10d202e7c81d28be4eb0ab98bf21e981e558f2e5179605bac</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>688.37615</t>
+          <t>15.81921</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786476767</t>
+          <t>1786490214</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1533.98585</t>
+          <t>35.44921</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
+          <t>0x2e03fcc3f7ecc087552ed1d69a1f8008e36e398bfe42ea205ce282f08f1c1340</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>13.87999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786476263</t>
+          <t>1786490114</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>73.723077</t>
+          <t>24.952791</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,12 +963,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
+          <t>0x031e42fbfd08a3c7d769259edbc4291e998075aee0ff949b46b2ff5a320f4fb9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3075</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786473059</t>
+          <t>1786487872</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>15.447154</t>
+          <t>3.62449</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,31 +1075,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
+          <t>0x973ce82e34197c696686774e4b32dc293666e3b1f344b3c042ea8e0bc0baf472</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.2463</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1122,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786466862</t>
+          <t>1786484906</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>586.482759</t>
+          <t>12.182741</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,31 +1187,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
+          <t>0x4189c1704e3efda1c32f863bee5edac536cbbc1ddc5c7ff92ffcec3f8671f4dd</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1226,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1256,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786466015</t>
+          <t>1786483830</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1266,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>16.675105</t>
+          <t>9.433962</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
+          <t>0x86035074a77352f25945be3c07a1ce0a72476812a4d9ee7a5d31accc0005ca8e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1298,22 +1314,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>119.23</t>
+          <t>2.14549</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1338,7 +1354,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1368,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786465613</t>
+          <t>1786483821</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>662.388889</t>
+          <t>4.06728</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,28 +1411,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
+          <t>0x95d1a72bec5f6cbef6a0bee578fc49d11315543f98d64986bc30ab10b98ab235</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.6987</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1442,7 +1458,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1472,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786462484</t>
+          <t>1786481014</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>24.911111</t>
+          <t>429.338104</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,62 +1515,54 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
+          <t>0x75abf2cc9245d94d8697557465991a972b17d428172f9c86e5103ccf4513ae1d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23.9188</t>
+          <t>280.65999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1584,7 +1592,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786460921</t>
+          <t>1786479821</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1602,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>111.250233</t>
+          <t>400.942843</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,31 +1619,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
+          <t>0x7b6931100ecd01485a88a37e39d7604129b6c1b4774ef01d18474422b8022991</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>295.34</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1658,7 +1674,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1688,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786459823</t>
+          <t>1786479008</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3.232323</t>
+          <t>1211.651282</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,28 +1731,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
+          <t>0xfd5730799b860d55deb75e792b32577fe97b21a6872bcdcae76b7d727aa3f5e1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>15.78675</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1762,7 +1778,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1792,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786459704</t>
+          <t>1786478908</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>343.089431</t>
+          <t>35.475843</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,28 +1835,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
+          <t>0xaa6b20356dec3ef3de3c3740df5cda0bfaf51ac484d1b2f78d6d001ebf63c609</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>280.99999</t>
+          <t>0.00327</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.7675</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1866,7 +1882,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1896,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786459347</t>
+          <t>1786478826</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>456.910553</t>
+          <t>0.004261</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
+          <t>0x1ca2c2e3faa5fd0586c76f29023f0ae32e5b7eb91a5e924bff0c79c1fd8e3978</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1931,23 +1947,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>312.25</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1970,7 +1994,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2000,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786431942</t>
+          <t>1786478809</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2010,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>647.150259</t>
+          <t>31.220513</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,27 +2051,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+          <t>0xd719c5ae636d9e747b1caa23c9df7ac916d22589ebafce09e6a90f528305ad43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.00999</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2055,26 +2075,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -2082,7 +2098,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2112,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786424623</t>
+          <t>1786478807</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2122,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>10.977151</t>
+          <t>39.736842</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2139,31 +2155,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+          <t>0x7e152d80b0c185c0abe8c4ca426947b4261d81003670d3822de824587a968e1d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5637</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2186,7 +2210,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2216,7 +2240,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786421953</t>
+          <t>1786478806</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2226,7 +2250,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.040816</t>
+          <t>49.507761</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2243,31 +2267,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+          <t>0x762726fa569798e9bb38e6d1d3a6718a3e6b17854ec943996f440407d07d5af1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>30.51955</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2290,7 +2322,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2320,7 +2352,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786421917</t>
+          <t>1786478801</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2330,7 +2362,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>138.77551</t>
+          <t>148.875854</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,31 +2379,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+          <t>0x8e47fef69d97d7a182f242c2cdce1afab730128f4310cd28a6f9c5d37adae0d1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>36.47459</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.245</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2394,7 +2434,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2424,7 +2464,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786421886</t>
+          <t>1786478798</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2434,7 +2474,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>18.414322</t>
+          <t>148.875878</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2451,28 +2491,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0x4b13bf02996be9f8f2f945b0a566bfd6a4a430bd57ac43a76f92d64f15f5498d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>66.06366</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2498,7 +2538,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2528,7 +2568,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786478774</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2538,7 +2578,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>148.875854</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,39 +2595,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0xe9e3237227be288d77eb896c110ca16fd4018525f8bcea0d1e30930f9032da8b</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>2.10999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2610,7 +2642,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2640,7 +2672,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786478768</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2650,7 +2682,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>2.776303</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,12 +2699,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x4c9eb0ce8768b1300644ee9d6d756f3477ae0a67da7b2d98350ea8c35a646255</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2682,22 +2714,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2722,7 +2754,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2752,7 +2784,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786478575</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2762,7 +2794,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>23.786192</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,27 +2811,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x3991dd65a93f5a305e8899432f4bb1612f1b874d3aa09a9a9266778002ba1f22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>280.97998</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2807,26 +2835,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -2834,7 +2858,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2864,7 +2888,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786478575</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2874,7 +2898,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>369.7105</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,12 +2915,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2906,12 +2930,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2921,32 +2945,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2976,7 +3000,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786477844</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2986,7 +3010,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>44.882051</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3003,23 +3027,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3050,7 +3074,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3080,7 +3104,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786477225</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3090,7 +3114,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>6016.713092</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3107,23 +3131,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>688.37615</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3154,7 +3178,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3184,7 +3208,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786476767</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3194,7 +3218,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>1533.98585</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3211,23 +3235,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3235,7 +3263,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3258,7 +3290,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3288,7 +3320,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786476263</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3298,7 +3330,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>73.723077</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3315,7 +3347,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3323,23 +3355,31 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.3075</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3362,7 +3402,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3392,7 +3432,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786473059</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3402,7 +3442,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>15.447154</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3419,39 +3459,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3474,7 +3506,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3504,7 +3536,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786466862</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3514,7 +3546,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>586.482759</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3531,39 +3563,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3586,7 +3610,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3616,7 +3640,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786466015</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3626,7 +3650,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>16.675105</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3643,7 +3667,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3658,12 +3682,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>119.23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3728,7 +3752,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786465613</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3738,7 +3762,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>662.388889</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3755,28 +3779,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UEFA Super Cup</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3802,7 +3826,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3832,7 +3856,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786462484</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3842,7 +3866,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>24.911111</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3859,12 +3883,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3874,12 +3898,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>23.9188</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3944,7 +3968,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786460921</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3954,7 +3978,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>111.250233</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3971,110 +3995,2470 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.6187</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1786459823</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>3.232323</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.615</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1786459704</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>343.089431</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>280.99999</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.615</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1786459347</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>456.910553</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>312.25</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.4825</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1786431942</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>647.150259</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>6.00999</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.5475</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1786424623</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>10.977151</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1786421953</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2.040816</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1786421917</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>138.77551</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.4888</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1786421886</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>18.414322</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>216.99999</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.4888</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1786409895</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>443.989749</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13.13154</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.065</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1786390904</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>202.023692</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>11.30985</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.065</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1786390902</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>173.997692</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>12.49</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.5475</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1786371203</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>22.812785</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1786334647</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>13.872832</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1786316612</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1786316590</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>331.57222</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1786316229</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>415.11389</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>20.70997</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1786316213</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>26.009381</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>74.68</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1786310047</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>206.726644</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>65.17485</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1786309443</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>87.48302</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x5e9b92a3ee864ed306ae19b1eb8415371da432df1801adf9df4096158c2ada97</t>
+          <t>0xdac326f5927fbb970e6253d4f41b0dda53f675cb5449d4ce88a3392cdb3f18d2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.15226</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.3975</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786491019</t>
+          <t>1786499763</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>49.502257</t>
+          <t>49.207547</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x23733dbdf9fa3729981e360673c4b7d7c10ff2531e371c5badad3796d6c9c512</t>
+          <t>0xe4d62db20d7dce5a6d3aba1b5840a8cfadcc44c5e125c97cb74db1289ff05051</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,31 +651,23 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.55999</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -690,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x79833fc6a3f6648404ca4b99628add02ce86c2c2d0053296c7e23bea43b238d1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786490560</t>
+          <t>1786498202</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>49.43496</t>
+          <t>21.408451</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,23 +747,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x0727088f0a4a30c10d202e7c81d28be4eb0ab98bf21e981e558f2e5179605bac</t>
+          <t>0x7dcf5f848d78758aa81a9026f7a2af5c72cc084687859ec7c1750f509bdc420b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.81921</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -771,7 +775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -824,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786490214</t>
+          <t>1786496166</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35.44921</t>
+          <t>10.511211</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x2e03fcc3f7ecc087552ed1d69a1f8008e36e398bfe42ea205ce282f08f1c1340</t>
+          <t>0x42cfdc40991be588eb224c94dbbda3512b84f29d8a76e0e819f1717e16ea7f3a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -866,39 +874,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13.87999</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -906,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786490114</t>
+          <t>1786496166</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>24.952791</t>
+          <t>49.348946</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,39 +971,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x031e42fbfd08a3c7d769259edbc4291e998075aee0ff949b46b2ff5a320f4fb9</t>
+          <t>0xfafaa95fa892b7b96feb25237a96968c1542b373c172067c131656aed4764872</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>22.08887</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786487872</t>
+          <t>1786495559</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3.62449</t>
+          <t>49.498868</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,27 +1075,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x973ce82e34197c696686774e4b32dc293666e3b1f344b3c042ea8e0bc0baf472</t>
+          <t>0x2e1abfbad55d92ecb1113f9023da45bba5096910055bdcd79fd58fee8ad506ef</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14.82799</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2463</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1103,11 +1099,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1130,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786484906</t>
+          <t>1786495559</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>12.182741</t>
+          <t>33.227989</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,12 +1179,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x4189c1704e3efda1c32f863bee5edac536cbbc1ddc5c7ff92ffcec3f8671f4dd</t>
+          <t>0xda319e704a52e8ad3239c54f090757c46923aed8a6229dbb1a47a6aafdacc178</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1202,22 +1194,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.14999</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1242,7 +1234,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786483830</t>
+          <t>1786494130</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>9.433962</t>
+          <t>2.04898</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,12 +1291,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x86035074a77352f25945be3c07a1ce0a72476812a4d9ee7a5d31accc0005ca8e</t>
+          <t>0xe8544bdaf431d2b9cded859bb44c95e9a4cbb77d283569ab427748adf7c38a82</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1314,22 +1306,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.14549</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1354,7 +1346,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1384,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786483821</t>
+          <t>1786494129</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1394,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>4.06728</t>
+          <t>8.232143</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1411,31 +1403,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x95d1a72bec5f6cbef6a0bee578fc49d11315543f98d64986bc30ab10b98ab235</t>
+          <t>0x9f99840ce6a1d8f4c6f24f53d1e8ba96ef427cfa8f43a387601bdf53f416e3a4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6987</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786481014</t>
+          <t>1786494097</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>429.338104</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,31 +1515,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x75abf2cc9245d94d8697557465991a972b17d428172f9c86e5103ccf4513ae1d</t>
+          <t>0x17444d1a79b59787a6df8c716bc91f6b83490b852e7a42e1da13278178bd0fa3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>280.65999</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1562,7 +1570,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1592,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786479821</t>
+          <t>1786494077</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1602,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>400.942843</t>
+          <t>28.986547</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x7b6931100ecd01485a88a37e39d7604129b6c1b4774ef01d18474422b8022991</t>
+          <t>0xed62cce657564c54cdf4505d1beb541e7bb3559d7e8dafcf5c91e22df2dab644</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1634,7 +1642,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>295.34</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1704,7 +1712,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786479008</t>
+          <t>1786494054</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1714,7 +1722,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1211.651282</t>
+          <t>58.54359</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,28 +1739,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xfd5730799b860d55deb75e792b32577fe97b21a6872bcdcae76b7d727aa3f5e1</t>
+          <t>0x5e9b92a3ee864ed306ae19b1eb8415371da432df1801adf9df4096158c2ada97</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15.78675</t>
+          <t>22.15226</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1778,7 +1786,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1816,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786478908</t>
+          <t>1786491019</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1826,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>35.475843</t>
+          <t>49.502257</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,31 +1843,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xaa6b20356dec3ef3de3c3740df5cda0bfaf51ac484d1b2f78d6d001ebf63c609</t>
+          <t>0x23733dbdf9fa3729981e360673c4b7d7c10ff2531e371c5badad3796d6c9c512</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.00327</t>
+          <t>27.55999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.7675</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1882,7 +1898,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1928,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786478826</t>
+          <t>1786490560</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1938,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.004261</t>
+          <t>49.43496</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,27 +1955,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x1ca2c2e3faa5fd0586c76f29023f0ae32e5b7eb91a5e924bff0c79c1fd8e3978</t>
+          <t>0x0727088f0a4a30c10d202e7c81d28be4eb0ab98bf21e981e558f2e5179605bac</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>15.81921</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1967,11 +1979,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1994,7 +2002,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2024,7 +2032,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786478809</t>
+          <t>1786490214</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2034,7 +2042,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>31.220513</t>
+          <t>35.44921</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,23 +2059,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xd719c5ae636d9e747b1caa23c9df7ac916d22589ebafce09e6a90f528305ad43</t>
+          <t>0x2e03fcc3f7ecc087552ed1d69a1f8008e36e398bfe42ea205ce282f08f1c1340</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>13.87999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2075,7 +2087,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2098,7 +2114,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2128,7 +2144,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786478807</t>
+          <t>1786490114</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2154,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>39.736842</t>
+          <t>24.952791</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,7 +2171,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x7e152d80b0c185c0abe8c4ca426947b4261d81003670d3822de824587a968e1d</t>
+          <t>0x031e42fbfd08a3c7d769259edbc4291e998075aee0ff949b46b2ff5a320f4fb9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2170,22 +2186,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5637</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2210,7 +2226,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2240,7 +2256,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786478806</t>
+          <t>1786487872</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2250,7 +2266,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>49.507761</t>
+          <t>3.62449</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2267,12 +2283,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x762726fa569798e9bb38e6d1d3a6718a3e6b17854ec943996f440407d07d5af1</t>
+          <t>0x973ce82e34197c696686774e4b32dc293666e3b1f344b3c042ea8e0bc0baf472</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2282,12 +2298,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>30.51955</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.2463</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2297,32 +2313,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2352,7 +2368,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786478801</t>
+          <t>1786484906</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2362,7 +2378,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>148.875854</t>
+          <t>12.182741</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2379,12 +2395,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x8e47fef69d97d7a182f242c2cdce1afab730128f4310cd28a6f9c5d37adae0d1</t>
+          <t>0x4189c1704e3efda1c32f863bee5edac536cbbc1ddc5c7ff92ffcec3f8671f4dd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2394,22 +2410,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36.47459</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2434,7 +2450,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2464,7 +2480,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786478798</t>
+          <t>1786483830</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2474,7 +2490,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>148.875878</t>
+          <t>9.433962</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2491,31 +2507,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x4b13bf02996be9f8f2f945b0a566bfd6a4a430bd57ac43a76f92d64f15f5498d</t>
+          <t>0x86035074a77352f25945be3c07a1ce0a72476812a4d9ee7a5d31accc0005ca8e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>66.06366</t>
+          <t>2.14549</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2538,7 +2562,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2568,7 +2592,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786478774</t>
+          <t>1786483821</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2578,7 +2602,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>148.875854</t>
+          <t>4.06728</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2595,28 +2619,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xe9e3237227be288d77eb896c110ca16fd4018525f8bcea0d1e30930f9032da8b</t>
+          <t>0x95d1a72bec5f6cbef6a0bee578fc49d11315543f98d64986bc30ab10b98ab235</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.10999</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.6987</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2642,7 +2666,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2672,7 +2696,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786478768</t>
+          <t>1786481014</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2682,7 +2706,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2.776303</t>
+          <t>429.338104</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2699,7 +2723,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x4c9eb0ce8768b1300644ee9d6d756f3477ae0a67da7b2d98350ea8c35a646255</t>
+          <t>0x75abf2cc9245d94d8697557465991a972b17d428172f9c86e5103ccf4513ae1d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2707,46 +2731,38 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>280.65999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -2754,7 +2770,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2784,7 +2800,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786478575</t>
+          <t>1786479821</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2794,7 +2810,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>23.786192</t>
+          <t>400.942843</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,23 +2827,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x3991dd65a93f5a305e8899432f4bb1612f1b874d3aa09a9a9266778002ba1f22</t>
+          <t>0x7b6931100ecd01485a88a37e39d7604129b6c1b4774ef01d18474422b8022991</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>280.97998</t>
+          <t>295.34</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2835,7 +2855,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2888,7 +2912,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786478575</t>
+          <t>1786479008</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2898,7 +2922,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>369.7105</t>
+          <t>1211.651282</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,27 +2939,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
+          <t>0xfd5730799b860d55deb75e792b32577fe97b21a6872bcdcae76b7d727aa3f5e1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>15.78675</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2943,11 +2963,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2970,7 +2986,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3000,7 +3016,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786477844</t>
+          <t>1786478908</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3010,7 +3026,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>44.882051</t>
+          <t>35.475843</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3027,23 +3043,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
+          <t>0xaa6b20356dec3ef3de3c3740df5cda0bfaf51ac484d1b2f78d6d001ebf63c609</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>0.00327</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.7675</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3074,7 +3090,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3104,7 +3120,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786477225</t>
+          <t>1786478826</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3114,7 +3130,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>6016.713092</t>
+          <t>0.004261</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3131,23 +3147,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
+          <t>0x1ca2c2e3faa5fd0586c76f29023f0ae32e5b7eb91a5e924bff0c79c1fd8e3978</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>688.37615</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3155,7 +3175,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3178,7 +3202,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3208,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786476767</t>
+          <t>1786478809</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3218,7 +3242,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1533.98585</t>
+          <t>31.220513</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3235,27 +3259,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
+          <t>0xd719c5ae636d9e747b1caa23c9df7ac916d22589ebafce09e6a90f528305ad43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3263,11 +3283,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3320,7 +3336,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786476263</t>
+          <t>1786478807</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3330,7 +3346,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>73.723077</t>
+          <t>39.736842</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3347,12 +3363,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
+          <t>0x7e152d80b0c185c0abe8c4ca426947b4261d81003670d3822de824587a968e1d</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3362,22 +3378,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3075</t>
+          <t>1.5637</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3402,7 +3418,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3432,7 +3448,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786473059</t>
+          <t>1786478806</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3442,7 +3458,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>15.447154</t>
+          <t>49.507761</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3459,31 +3475,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
+          <t>0x762726fa569798e9bb38e6d1d3a6718a3e6b17854ec943996f440407d07d5af1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>30.51955</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3506,7 +3530,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3536,7 +3560,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786466862</t>
+          <t>1786478801</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3546,7 +3570,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>586.482759</t>
+          <t>148.875854</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3563,31 +3587,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
+          <t>0x8e47fef69d97d7a182f242c2cdce1afab730128f4310cd28a6f9c5d37adae0d1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>36.47459</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.245</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3610,7 +3642,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3640,7 +3672,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786466015</t>
+          <t>1786478798</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3650,7 +3682,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>16.675105</t>
+          <t>148.875878</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3667,39 +3699,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
+          <t>0x4b13bf02996be9f8f2f945b0a566bfd6a4a430bd57ac43a76f92d64f15f5498d</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>119.23</t>
+          <t>66.06366</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3722,7 +3746,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3752,7 +3776,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786465613</t>
+          <t>1786478774</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3762,7 +3786,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>662.388889</t>
+          <t>148.875854</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3779,23 +3803,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
+          <t>0xe9e3237227be288d77eb896c110ca16fd4018525f8bcea0d1e30930f9032da8b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>2.10999</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3826,7 +3850,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3856,7 +3880,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786462484</t>
+          <t>1786478768</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3866,7 +3890,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>24.911111</t>
+          <t>2.776303</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3883,12 +3907,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
+          <t>0x4c9eb0ce8768b1300644ee9d6d756f3477ae0a67da7b2d98350ea8c35a646255</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3898,12 +3922,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23.9188</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3913,32 +3937,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3968,7 +3992,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786460921</t>
+          <t>1786478575</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3978,7 +4002,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>111.250233</t>
+          <t>23.786192</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3995,28 +4019,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
+          <t>0x3991dd65a93f5a305e8899432f4bb1612f1b874d3aa09a9a9266778002ba1f22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>280.97998</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -4042,7 +4066,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4072,7 +4096,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786459823</t>
+          <t>1786478575</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4082,7 +4106,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>3.232323</t>
+          <t>369.7105</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4099,31 +4123,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
+          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4146,7 +4178,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4176,7 +4208,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786459704</t>
+          <t>1786477844</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4186,7 +4218,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>343.089431</t>
+          <t>44.882051</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4203,28 +4235,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
+          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
+          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>280.99999</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4250,7 +4282,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4280,7 +4312,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786459347</t>
+          <t>1786477225</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4290,7 +4322,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>456.910553</t>
+          <t>6016.713092</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4307,28 +4339,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
+          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>312.25</t>
+          <t>688.37615</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4354,7 +4386,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4384,7 +4416,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786431942</t>
+          <t>1786476767</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4394,7 +4426,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>647.150259</t>
+          <t>1533.98585</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4411,12 +4443,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4426,12 +4458,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>6.00999</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4441,24 +4473,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -4466,7 +4498,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4496,7 +4528,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786424623</t>
+          <t>1786476263</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4506,7 +4538,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>10.977151</t>
+          <t>73.723077</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4523,31 +4555,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.3075</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4570,7 +4610,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4600,7 +4640,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786421953</t>
+          <t>1786473059</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4610,7 +4650,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2.040816</t>
+          <t>15.447154</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4627,28 +4667,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4674,7 +4714,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4704,7 +4744,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786421917</t>
+          <t>1786466862</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4714,7 +4754,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>138.77551</t>
+          <t>586.482759</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4731,28 +4771,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4778,7 +4818,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4808,7 +4848,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786421886</t>
+          <t>1786466015</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4818,7 +4858,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>18.414322</t>
+          <t>16.675105</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4835,31 +4875,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>119.23</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4882,7 +4930,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4912,7 +4960,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786465613</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4922,7 +4970,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>662.388889</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4939,39 +4987,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4994,7 +5034,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5024,7 +5064,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786462484</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5034,7 +5074,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>24.911111</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5051,12 +5091,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5066,22 +5106,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>23.9188</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5106,7 +5146,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5136,7 +5176,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786460921</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5146,7 +5186,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>111.250233</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5163,54 +5203,46 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -5218,7 +5250,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5248,7 +5280,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786459823</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5258,7 +5290,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>3.232323</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5275,62 +5307,54 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5360,7 +5384,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786459704</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5370,7 +5394,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>343.089431</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5387,28 +5411,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>280.99999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5434,7 +5458,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5464,7 +5488,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786459347</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5474,7 +5498,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>456.910553</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5491,28 +5515,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>312.25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4825</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5538,7 +5562,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5568,7 +5592,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786431942</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5578,7 +5602,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>647.150259</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5595,7 +5619,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5603,15 +5627,19 @@
           <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>6.00999</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5619,7 +5647,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5642,7 +5674,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5672,7 +5704,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786424623</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5682,7 +5714,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>10.977151</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5699,28 +5731,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5746,7 +5778,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5776,7 +5808,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786421953</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5786,7 +5818,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>2.040816</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5803,39 +5835,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5858,7 +5882,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5888,7 +5912,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786421917</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5898,7 +5922,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>138.77551</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5915,39 +5939,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5970,7 +5986,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6000,7 +6016,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786421886</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6010,7 +6026,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>18.414322</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6027,39 +6043,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>216.99999</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -6082,7 +6090,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6112,7 +6120,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786409895</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6122,7 +6130,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>443.989749</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6139,7 +6147,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6147,28 +6155,36 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>13.13154</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -6186,7 +6202,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6216,7 +6232,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786390904</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6226,7 +6242,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>202.023692</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6243,7 +6259,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6258,47 +6274,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>11.30985</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6328,7 +6344,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786390902</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6338,7 +6354,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>173.997692</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6355,110 +6371,1302 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>12.49</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.5475</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1786371203</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>22.812785</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1786334647</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>13.872832</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1786316612</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1786316590</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>331.57222</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1786316229</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>415.11389</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>20.70997</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1786316213</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>26.009381</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>74.68</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1786310047</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>206.726644</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>65.17485</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1786309443</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>87.48302</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V67"/>
+  <dimension ref="A1:V109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xdac326f5927fbb970e6253d4f41b0dda53f675cb5449d4ce88a3392cdb3f18d2</t>
+          <t>0xd780d195ce364dd621ce45379699b2c7994680570e51d0eca2c1ed1143572b62</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>1335.26</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3975</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786499763</t>
+          <t>1786501059</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>49.207547</t>
+          <t>2400.467416</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,36 +643,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xe4d62db20d7dce5a6d3aba1b5840a8cfadcc44c5e125c97cb74db1289ff05051</t>
+          <t>0x552df581fa9ee8db3d9033f3b2aae0d7a8a7e68bee7632a0f109eb9c8b3b8551</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -690,7 +698,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x79833fc6a3f6648404ca4b99628add02ce86c2c2d0053296c7e23bea43b238d1</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786498202</t>
+          <t>1786500980</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>21.408451</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x7dcf5f848d78758aa81a9026f7a2af5c72cc084687859ec7c1750f509bdc420b</t>
+          <t>0x135ca5b241b0d1e484c97d7c26d71e9d58e6dd971b22360ae9e62df23118ee6b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -762,39 +770,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -802,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786496166</t>
+          <t>1786500974</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>10.511211</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +867,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x42cfdc40991be588eb224c94dbbda3512b84f29d8a76e0e819f1717e16ea7f3a</t>
+          <t>0xd0e485c8a54ff92288008fc7ef998bfee28e3c9deabfed91f9266b54b7325639</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,22 +882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -914,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786496166</t>
+          <t>1786500803</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>49.348946</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,23 +979,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xfafaa95fa892b7b96feb25237a96968c1542b373c172067c131656aed4764872</t>
+          <t>0x32f75f1a679cbf6e5a754001684967d29f8331ea42c38c104d263619cd26bc14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22.08887</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -995,7 +1007,11 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1048,7 +1064,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786495559</t>
+          <t>1786500801</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1058,7 +1074,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>49.498868</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,31 +1091,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x2e1abfbad55d92ecb1113f9023da45bba5096910055bdcd79fd58fee8ad506ef</t>
+          <t>0xa4d6707462e7e71482a034711a024006ce64ad33f684e3ffc8aa48e105b8ad86</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.82799</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1122,7 +1146,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1176,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786495559</t>
+          <t>1786500799</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1186,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>33.227989</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,12 +1203,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xda319e704a52e8ad3239c54f090757c46923aed8a6229dbb1a47a6aafdacc178</t>
+          <t>0x3efe4e02ea3d9bfa26256cae2117b7deedc84fd159b4045c452040d9b1f2d7c5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,12 +1218,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.14999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1264,7 +1288,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786494130</t>
+          <t>1786500797</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1298,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2.04898</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,12 +1315,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe8544bdaf431d2b9cded859bb44c95e9a4cbb77d283569ab427748adf7c38a82</t>
+          <t>0xbc8939d03f5d2c19550a7b112bffcf5adc6d07378d6ceb670253bc89f48240b6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1306,39 +1330,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>187.21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -1346,7 +1370,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1400,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786494129</t>
+          <t>1786500775</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1410,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>8.232143</t>
+          <t>336.557303</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,12 +1427,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9f99840ce6a1d8f4c6f24f53d1e8ba96ef427cfa8f43a387601bdf53f416e3a4</t>
+          <t>0x9aab0146566e1cf2d904cec61e5fc8853c9b003f5b9a0f3c4e69d5d5b5c484ed</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1418,12 +1442,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>63.35999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1488,7 +1512,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786494097</t>
+          <t>1786500773</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1498,7 +1522,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>113.9056</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1515,12 +1539,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x17444d1a79b59787a6df8c716bc91f6b83490b852e7a42e1da13278178bd0fa3</t>
+          <t>0xf93ca08ba4c183f19691ac949364bf8e7941471d36502742e2371e46518e091f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1530,39 +1554,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -1570,7 +1594,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1600,7 +1624,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786494077</t>
+          <t>1786500761</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1610,7 +1634,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>28.986547</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,12 +1651,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xed62cce657564c54cdf4505d1beb541e7bb3559d7e8dafcf5c91e22df2dab644</t>
+          <t>0x81f5973a3f28d7aaeefe7911ffccf1e98af44fcaa930aeac34875dd38df71bc9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1642,22 +1666,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1682,7 +1706,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1712,7 +1736,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786494054</t>
+          <t>1786500760</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1722,7 +1746,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>58.54359</t>
+          <t>47.388764</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1739,23 +1763,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x5e9b92a3ee864ed306ae19b1eb8415371da432df1801adf9df4096158c2ada97</t>
+          <t>0x66eeaf3004065d2e62328224d064e8196d58379f132fedbd741c76858295a7f7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>22.15226</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1763,7 +1791,11 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1816,7 +1848,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786491019</t>
+          <t>1786500757</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1826,7 +1858,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>49.502257</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,12 +1875,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x23733dbdf9fa3729981e360673c4b7d7c10ff2531e371c5badad3796d6c9c512</t>
+          <t>0xbad5215a4edd54d38386bd1e5448631e76e90dbee3e4bf3557e8e2c043083418</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1858,12 +1890,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27.55999</t>
+          <t>104.21999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1928,7 +1960,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786490560</t>
+          <t>1786500752</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1938,7 +1970,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>49.43496</t>
+          <t>187.36178</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1955,7 +1987,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x0727088f0a4a30c10d202e7c81d28be4eb0ab98bf21e981e558f2e5179605bac</t>
+          <t>0xdd309ef6c0dc57692dec182e5cffcdd0c7f85c99189249002a5ee7c4793563d9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1963,23 +1995,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15.81921</t>
+          <t>83.09999</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2002,7 +2042,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2032,7 +2072,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786490214</t>
+          <t>1786500737</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2042,7 +2082,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>35.44921</t>
+          <t>149.39324</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2059,12 +2099,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x2e03fcc3f7ecc087552ed1d69a1f8008e36e398bfe42ea205ce282f08f1c1340</t>
+          <t>0x96136c19e8b4b3c1cd9a022ec3ec1be7af2fc0def6358940a3b219bccf20682d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2074,7 +2114,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.87999</t>
+          <t>47.21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2084,29 +2124,29 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -2114,7 +2154,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2144,7 +2184,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786490114</t>
+          <t>1786500736</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2154,7 +2194,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>24.952791</t>
+          <t>84.87191</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2171,39 +2211,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x031e42fbfd08a3c7d769259edbc4291e998075aee0ff949b46b2ff5a320f4fb9</t>
+          <t>0x7b50006545a4d3976ffc8f0762f94bd9fdff1567a3cf664dd9e79edf834c96bc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>197.75</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2226,7 +2258,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2256,7 +2288,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786487872</t>
+          <t>1786500644</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2266,7 +2298,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3.62449</t>
+          <t>444.382022</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,39 +2315,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x973ce82e34197c696686774e4b32dc293666e3b1f344b3c042ea8e0bc0baf472</t>
+          <t>0xf9e921304b5613d4f5a4aac94cdaeac732d8ea42bec44a92191306c7103df732</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>369.91</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2463</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2338,7 +2362,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2368,7 +2392,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786484906</t>
+          <t>1786500633</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2378,7 +2402,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>12.182741</t>
+          <t>831.258427</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,7 +2419,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x4189c1704e3efda1c32f863bee5edac536cbbc1ddc5c7ff92ffcec3f8671f4dd</t>
+          <t>0xdf4ba60566fd5689393750a08058e1a227b21e0bb2b7a75524dd08921158b328</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2415,17 +2439,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2450,7 +2474,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2480,7 +2504,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786483830</t>
+          <t>1786500582</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2490,7 +2514,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>9.433962</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2507,12 +2531,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x86035074a77352f25945be3c07a1ce0a72476812a4d9ee7a5d31accc0005ca8e</t>
+          <t>0x5e90c46cc93882168350f5e6b83523a3325a59dffb9497b35253b8552791e3ab</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2522,22 +2546,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.14549</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2562,7 +2586,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2592,7 +2616,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786483821</t>
+          <t>1786500580</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2602,7 +2626,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>4.06728</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2619,31 +2643,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x95d1a72bec5f6cbef6a0bee578fc49d11315543f98d64986bc30ab10b98ab235</t>
+          <t>0xa18586bdb3003365505e403bdf79edab1b8478a9e9e230f70c4e76fdf6d003cc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6987</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2666,7 +2698,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2696,7 +2728,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786481014</t>
+          <t>1786500551</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2706,7 +2738,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>429.338104</t>
+          <t>89.510112</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2723,31 +2755,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x75abf2cc9245d94d8697557465991a972b17d428172f9c86e5103ccf4513ae1d</t>
+          <t>0xcee60a04b8f8d5efba6d52111a13199c73c69fd54b9f9f9ba72592c359f92c6a</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>280.65999</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2770,7 +2810,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2800,7 +2840,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786479821</t>
+          <t>1786500550</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2810,7 +2850,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>400.942843</t>
+          <t>49.078652</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2827,12 +2867,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x7b6931100ecd01485a88a37e39d7604129b6c1b4774ef01d18474422b8022991</t>
+          <t>0x0909a65a14fd4ad7dbd184945e4e82c9fdce475552b31ac2ffa79f5cc8d2d2fc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2842,22 +2882,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>295.34</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2882,7 +2922,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2912,7 +2952,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786479008</t>
+          <t>1786500544</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2922,7 +2962,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1211.651282</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2939,31 +2979,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xfd5730799b860d55deb75e792b32577fe97b21a6872bcdcae76b7d727aa3f5e1</t>
+          <t>0xf47ded4743419e912443bb01778bf84bf92c70cb548340b8471b4e65e69d5d72</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15.78675</t>
+          <t>28.58</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2986,7 +3034,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3016,7 +3064,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786478908</t>
+          <t>1786500534</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3026,7 +3074,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>35.475843</t>
+          <t>51.379775</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3043,7 +3091,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xaa6b20356dec3ef3de3c3740df5cda0bfaf51ac484d1b2f78d6d001ebf63c609</t>
+          <t>0x944f5df4e4d993386c3114a59ad8704373224aae960b40c8fb5dc958868cd0c9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3051,23 +3099,31 @@
           <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.00327</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.7675</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3090,7 +3146,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3120,7 +3176,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786478826</t>
+          <t>1786500504</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3130,7 +3186,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.004261</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,12 +3203,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x1ca2c2e3faa5fd0586c76f29023f0ae32e5b7eb91a5e924bff0c79c1fd8e3978</t>
+          <t>0x4ffb70fc7ea797009babeaf3a2360c329a379a328dab0ce16fa709514d4f9cef</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3162,22 +3218,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3202,7 +3258,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3232,7 +3288,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786478809</t>
+          <t>1786500503</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3242,7 +3298,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>31.220513</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,31 +3315,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xd719c5ae636d9e747b1caa23c9df7ac916d22589ebafce09e6a90f528305ad43</t>
+          <t>0x5c7eb9a2501c32b896b5a9b685517d32cbfe67726fca300d63b10476842d2c2a</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3306,7 +3370,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3336,7 +3400,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786478807</t>
+          <t>1786500501</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3346,7 +3410,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>39.736842</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3363,12 +3427,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x7e152d80b0c185c0abe8c4ca426947b4261d81003670d3822de824587a968e1d</t>
+          <t>0x95e9e1a3038ffc59cdb49a206e8adcb19179a43073a098619bdd395c0570cb37</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3378,12 +3442,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5637</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3448,7 +3512,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786478806</t>
+          <t>1786500499</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3458,7 +3522,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>49.507761</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3475,12 +3539,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x762726fa569798e9bb38e6d1d3a6718a3e6b17854ec943996f440407d07d5af1</t>
+          <t>0x0d5cd46de2f58ac252c6a0489b2fb8253629014f2f6b91d710ba41e1803b36b8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3490,47 +3554,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>30.51955</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3560,7 +3624,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786478801</t>
+          <t>1786500498</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3570,7 +3634,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>148.875854</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3587,12 +3651,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x8e47fef69d97d7a182f242c2cdce1afab730128f4310cd28a6f9c5d37adae0d1</t>
+          <t>0x5294d64dc44b1c637243f3de9a061ba385cc84408b2ea0a98d2ddf6c6718815c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3602,22 +3666,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>36.47459</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3642,7 +3706,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3672,7 +3736,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786478798</t>
+          <t>1786500496</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3682,7 +3746,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>148.875878</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3699,31 +3763,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x4b13bf02996be9f8f2f945b0a566bfd6a4a430bd57ac43a76f92d64f15f5498d</t>
+          <t>0xb5ce2ecec5f0be7b0047ce88d13d0c9055b5fca8d9c11bc67e966280f2384598</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>66.06366</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3746,7 +3818,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3776,7 +3848,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786478774</t>
+          <t>1786500494</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3786,7 +3858,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>148.875854</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3803,31 +3875,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xe9e3237227be288d77eb896c110ca16fd4018525f8bcea0d1e30930f9032da8b</t>
+          <t>0x7c3b5079c34701a023626323d701dfc0a4e7823959dc0481793b08574dc9dfd1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.10999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3850,7 +3930,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3880,7 +3960,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786478768</t>
+          <t>1786500492</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3890,7 +3970,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.776303</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3907,12 +3987,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x4c9eb0ce8768b1300644ee9d6d756f3477ae0a67da7b2d98350ea8c35a646255</t>
+          <t>0xc25d80f3f8534bd014aa3041b4ded1b98e2b6f01f0f432a007e92f8d97721feb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3922,39 +4002,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -3962,7 +4042,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3992,7 +4072,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786478575</t>
+          <t>1786500491</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4002,7 +4082,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>23.786192</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4019,31 +4099,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x3991dd65a93f5a305e8899432f4bb1612f1b874d3aa09a9a9266778002ba1f22</t>
+          <t>0x4b0fefa802aee78ae049407556ceab6fc43dd1967b5944a825593c40843bea6d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>280.97998</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4066,7 +4154,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4096,7 +4184,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786478575</t>
+          <t>1786500476</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4106,7 +4194,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>369.7105</t>
+          <t>66.570787</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4123,12 +4211,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
+          <t>0x8e07b84ce6844c38bd99c9ded59e55289f96bab45374d6cafd8039a6848c3ae1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4138,22 +4226,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>132.26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4178,7 +4266,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4208,7 +4296,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786477844</t>
+          <t>1786500474</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4218,7 +4306,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>44.882051</t>
+          <t>237.770787</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4235,31 +4323,39 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
+          <t>0x0aea6283317d83074694b78f764d29c7b95d51f4e307b7019541bd6400e1a8b8</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>76.86</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4282,7 +4378,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4312,7 +4408,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786477225</t>
+          <t>1786500468</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4322,7 +4418,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>6016.713092</t>
+          <t>138.175281</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4339,31 +4435,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
+          <t>0xdda980bbea51d427848750fa29aa6f27e23db79e2c7c5629a9587f9bde755ba9</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>688.37615</t>
+          <t>77.35999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4386,7 +4490,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4416,7 +4520,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786476767</t>
+          <t>1786500460</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4426,7 +4530,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1533.98585</t>
+          <t>139.074139</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4443,12 +4547,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
+          <t>0xe29c36778555e41d28b19553e722e94874412123ccb1bedea115d69ba68e5e12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4458,22 +4562,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>41.10999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4498,7 +4602,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4528,7 +4632,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786476263</t>
+          <t>1786500458</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4538,7 +4642,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>73.723077</t>
+          <t>73.9056</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4555,12 +4659,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
+          <t>0x29146d1a0dbde03d831d263bc99690b03cefcdfa8dc20dedd782669d6c9213f9</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4570,22 +4674,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>120.74</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.3075</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4610,7 +4714,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4640,7 +4744,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786473059</t>
+          <t>1786500456</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4650,7 +4754,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>15.447154</t>
+          <t>217.060674</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4667,31 +4771,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
+          <t>0x7bc5af8f4863cacf664ab30c084a2a43acfbcc9eff568595a2106ce23da17209</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4714,7 +4826,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4744,7 +4856,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786466862</t>
+          <t>1786500454</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4754,7 +4866,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>586.482759</t>
+          <t>49.222472</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4771,31 +4883,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
+          <t>0x5ae0620d3e7fd0d39c61c92d92dff0f44ffb8e289337ebe156f3686d570026cf</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>114.08</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4818,7 +4938,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4848,7 +4968,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786466015</t>
+          <t>1786500453</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4858,7 +4978,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>16.675105</t>
+          <t>205.08764</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4875,7 +4995,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
+          <t>0xf59e1f15c89fd009ceb1441f549470bd61d335d24c57df7a653f34a3fed23904</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4890,22 +5010,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>119.23</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Over 4.0</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4930,7 +5050,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4960,7 +5080,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786465613</t>
+          <t>1786500452</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4970,7 +5090,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>662.388889</t>
+          <t>75.595506</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4987,31 +5107,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
+          <t>0x7d734049fc9657458d52a381d19fb7d4aff8c4e71148efedd691e610e3a7a0bb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>1005.29</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5034,7 +5162,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -5064,7 +5192,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786462484</t>
+          <t>1786500451</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5074,7 +5202,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>24.911111</t>
+          <t>1807.262921</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5091,12 +5219,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
+          <t>0xdac326f5927fbb970e6253d4f41b0dda53f675cb5449d4ce88a3392cdb3f18d2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5106,47 +5234,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>23.9188</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.3975</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5176,7 +5304,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786460921</t>
+          <t>1786499763</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5186,7 +5314,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>111.250233</t>
+          <t>49.207547</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5203,28 +5331,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
+          <t>0xe4d62db20d7dce5a6d3aba1b5840a8cfadcc44c5e125c97cb74db1289ff05051</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>UEFA Super Cup</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5250,7 +5378,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x79833fc6a3f6648404ca4b99628add02ce86c2c2d0053296c7e23bea43b238d1</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5280,7 +5408,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786459823</t>
+          <t>1786498202</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5290,7 +5418,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>3.232323</t>
+          <t>21.408451</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5307,31 +5435,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
+          <t>0x7dcf5f848d78758aa81a9026f7a2af5c72cc084687859ec7c1750f509bdc420b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5354,7 +5490,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5384,7 +5520,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786459704</t>
+          <t>1786496166</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5394,7 +5530,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>343.089431</t>
+          <t>10.511211</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5411,31 +5547,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
+          <t>0x42cfdc40991be588eb224c94dbbda3512b84f29d8a76e0e819f1717e16ea7f3a</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>280.99999</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5458,7 +5602,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5488,7 +5632,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786459347</t>
+          <t>1786496166</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5498,7 +5642,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>456.910553</t>
+          <t>49.348946</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5515,28 +5659,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
+          <t>0xfafaa95fa892b7b96feb25237a96968c1542b373c172067c131656aed4764872</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>312.25</t>
+          <t>22.08887</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5562,7 +5706,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5592,7 +5736,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786431942</t>
+          <t>1786495559</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5602,7 +5746,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>647.150259</t>
+          <t>49.498868</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5619,27 +5763,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+          <t>0x2e1abfbad55d92ecb1113f9023da45bba5096910055bdcd79fd58fee8ad506ef</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6.00999</t>
+          <t>14.82799</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5647,26 +5787,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -5704,7 +5840,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786424623</t>
+          <t>1786495559</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5714,7 +5850,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>10.977151</t>
+          <t>33.227989</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5731,31 +5867,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+          <t>0xda319e704a52e8ad3239c54f090757c46923aed8a6229dbb1a47a6aafdacc178</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.14999</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5778,7 +5922,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5808,7 +5952,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786421953</t>
+          <t>1786494130</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5818,7 +5962,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2.040816</t>
+          <t>2.04898</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5835,31 +5979,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+          <t>0xe8544bdaf431d2b9cded859bb44c95e9a4cbb77d283569ab427748adf7c38a82</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5882,7 +6034,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5912,7 +6064,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786421917</t>
+          <t>1786494129</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5922,7 +6074,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>138.77551</t>
+          <t>8.232143</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5939,31 +6091,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+          <t>0x9f99840ce6a1d8f4c6f24f53d1e8ba96ef427cfa8f43a387601bdf53f416e3a4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5986,7 +6146,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6016,7 +6176,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786421886</t>
+          <t>1786494097</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6026,7 +6186,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>18.414322</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6043,31 +6203,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0x17444d1a79b59787a6df8c716bc91f6b83490b852e7a42e1da13278178bd0fa3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -6090,7 +6258,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6120,7 +6288,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786494077</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6130,7 +6298,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>28.986547</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6147,12 +6315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0xed62cce657564c54cdf4505d1beb541e7bb3559d7e8dafcf5c91e22df2dab644</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6162,22 +6330,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6202,7 +6370,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6232,7 +6400,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786494054</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6242,7 +6410,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>58.54359</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6259,7 +6427,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x5e9b92a3ee864ed306ae19b1eb8415371da432df1801adf9df4096158c2ada97</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6267,31 +6435,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>22.15226</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -6314,7 +6474,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -6344,7 +6504,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786491019</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6354,7 +6514,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>49.502257</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6371,7 +6531,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x23733dbdf9fa3729981e360673c4b7d7c10ff2531e371c5badad3796d6c9c512</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6386,39 +6546,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>27.55999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K56" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -6426,7 +6586,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6456,7 +6616,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786490560</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6466,7 +6626,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>49.43496</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6483,27 +6643,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0x0727088f0a4a30c10d202e7c81d28be4eb0ab98bf21e981e558f2e5179605bac</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15.81921</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6511,34 +6667,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6568,7 +6720,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786490214</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6578,7 +6730,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>35.44921</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6595,23 +6747,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0x2e03fcc3f7ecc087552ed1d69a1f8008e36e398bfe42ea205ce282f08f1c1340</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>13.87999</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6619,7 +6775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -6642,7 +6802,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6672,7 +6832,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786490114</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6682,7 +6842,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>24.952791</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6699,31 +6859,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0x031e42fbfd08a3c7d769259edbc4291e998075aee0ff949b46b2ff5a320f4fb9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -6746,7 +6914,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6776,7 +6944,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786487872</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6786,7 +6954,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>3.62449</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6803,23 +6971,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x973ce82e34197c696686774e4b32dc293666e3b1f344b3c042ea8e0bc0baf472</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.2463</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6827,7 +6999,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -6850,7 +7026,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6880,7 +7056,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786484906</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6890,7 +7066,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>12.182741</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6907,31 +7083,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0x4189c1704e3efda1c32f863bee5edac536cbbc1ddc5c7ff92ffcec3f8671f4dd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -6954,7 +7138,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6984,7 +7168,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786483830</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6994,7 +7178,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>9.433962</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7011,7 +7195,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0x86035074a77352f25945be3c07a1ce0a72476812a4d9ee7a5d31accc0005ca8e</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7026,22 +7210,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>2.14549</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7066,7 +7250,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7096,7 +7280,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786483821</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7106,7 +7290,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>4.06728</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7123,39 +7307,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0x95d1a72bec5f6cbef6a0bee578fc49d11315543f98d64986bc30ab10b98ab235</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.6987</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -7178,7 +7354,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7208,7 +7384,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786481014</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7218,7 +7394,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>429.338104</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7235,39 +7411,31 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0x75abf2cc9245d94d8697557465991a972b17d428172f9c86e5103ccf4513ae1d</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>280.65999</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -7290,7 +7458,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7320,7 +7488,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786479821</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7330,7 +7498,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>400.942843</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7347,36 +7515,44 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0x7b6931100ecd01485a88a37e39d7604129b6c1b4774ef01d18474422b8022991</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>295.34</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -7394,7 +7570,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7424,7 +7600,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786479008</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7434,7 +7610,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>1211.651282</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7451,27 +7627,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xfd5730799b860d55deb75e792b32577fe97b21a6872bcdcae76b7d727aa3f5e1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>15.78675</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7479,34 +7651,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7536,7 +7704,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786478908</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7546,7 +7714,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>35.475843</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7563,110 +7731,4630 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>0xaa6b20356dec3ef3de3c3740df5cda0bfaf51ac484d1b2f78d6d001ebf63c609</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>0.00327</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.7675</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1786478826</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>0.004261</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x1ca2c2e3faa5fd0586c76f29023f0ae32e5b7eb91a5e924bff0c79c1fd8e3978</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.2437</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1786478809</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>31.220513</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0xd719c5ae636d9e747b1caa23c9df7ac916d22589ebafce09e6a90f528305ad43</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>30.2</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1786478807</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>39.736842</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x7e152d80b0c185c0abe8c4ca426947b4261d81003670d3822de824587a968e1d</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>27.91</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.5637</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1786478806</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>49.507761</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x762726fa569798e9bb38e6d1d3a6718a3e6b17854ec943996f440407d07d5af1</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>30.51955</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.205</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1786478801</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>148.875854</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x8e47fef69d97d7a182f242c2cdce1afab730128f4310cd28a6f9c5d37adae0d1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>36.47459</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.245</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1786478798</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>148.875878</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x4b13bf02996be9f8f2f945b0a566bfd6a4a430bd57ac43a76f92d64f15f5498d</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>66.06366</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.4438</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1786478774</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>148.875854</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0xe9e3237227be288d77eb896c110ca16fd4018525f8bcea0d1e30930f9032da8b</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2.10999</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1786478768</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>2.776303</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0x4c9eb0ce8768b1300644ee9d6d756f3477ae0a67da7b2d98350ea8c35a646255</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>13.35</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.5613</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1786478575</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>23.786192</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0x3991dd65a93f5a305e8899432f4bb1612f1b874d3aa09a9a9266778002ba1f22</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>280.97998</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1786478575</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>369.7105</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>10.94</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.2437</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1786477844</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>44.882051</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.4487</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1786477225</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>6016.713092</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>688.37615</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.4487</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1786476767</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1533.98585</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>17.97</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.2437</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1786476263</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>73.723077</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.3075</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1786473059</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>15.447154</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>42.52</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.0725</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1786466862</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>586.482759</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>9.88</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.5925</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1786466015</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>16.675105</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>119.23</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1786465613</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>662.388889</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>11.21</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1786462484</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>24.911111</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>23.9188</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.215</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1786460921</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>111.250233</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.6187</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1786459823</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>3.232323</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.615</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1786459704</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>343.089431</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>280.99999</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.615</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1786459347</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>456.910553</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>312.25</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.4825</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1786431942</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>647.150259</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>6.00999</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.5475</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1786424623</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>10.977151</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1786421953</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>2.040816</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1786421917</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>138.77551</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.4888</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1786421886</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>18.414322</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>216.99999</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.4888</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1786409895</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>443.989749</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>13.13154</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.065</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1786390904</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>202.023692</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>11.30985</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.065</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1786390902</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>173.997692</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>12.49</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.5475</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1786371203</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>22.812785</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1786334647</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>13.872832</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1786316612</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1786316590</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>331.57222</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>1786316229</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>415.11389</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>20.70997</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>1786316213</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>26.009381</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>74.68</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1786310047</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>206.726644</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>65.17485</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>1786309443</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>87.48302</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B109" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S109" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="T109" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="U109" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="V109" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V109"/>
+  <dimension ref="A1:V127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd780d195ce364dd621ce45379699b2c7994680570e51d0eca2c1ed1143572b62</t>
+          <t>0x0927d4c3e3931cdf9a37f03c0814f362709f2c0054156bff909783124cd97ba4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1335.26</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786501059</t>
+          <t>1786507172</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2400.467416</t>
+          <t>79.692308</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x552df581fa9ee8db3d9033f3b2aae0d7a8a7e68bee7632a0f109eb9c8b3b8551</t>
+          <t>0x9fddadee598b90df36d4beeaccd01cac540422762fccc11680d1a8c1c770bc25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +650,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.99999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -698,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786500980</t>
+          <t>1786506876</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>5.62059</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +747,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x135ca5b241b0d1e484c97d7c26d71e9d58e6dd971b22360ae9e62df23118ee6b</t>
+          <t>0xeaededa5eb1eec58e3a92c47dc6cb4169278932bfd131653a2a27ffed2fee2cd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,12 +762,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.5637</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -840,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786500974</t>
+          <t>1786506875</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>49.507761</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +859,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd0e485c8a54ff92288008fc7ef998bfee28e3c9deabfed91f9266b54b7325639</t>
+          <t>0x319d6fb0294ad8704b8abbe0d4e4c67f67b020f4d665c10e7219bac1dcba5ae9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,22 +874,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.7475</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>UEFA Super Cup</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -922,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -952,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786500803</t>
+          <t>1786506563</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -962,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>28.508361</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x32f75f1a679cbf6e5a754001684967d29f8331ea42c38c104d263619cd26bc14</t>
+          <t>0x2a712e8cbf8e60615d12ed5c38e599dff972e67ca964e58797cc9a64951d583f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -994,22 +986,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.4225</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Paris Saint Germain -1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1034,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1064,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786500801</t>
+          <t>1786506563</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1074,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>44.87574</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,39 +1083,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xa4d6707462e7e71482a034711a024006ce64ad33f684e3ffc8aa48e105b8ad86</t>
+          <t>0xade17fdc3c72bd54c67008038259583e24f46a47edddd5d0a65e7780edf4f60b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10.12537</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.2637</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1146,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x79833fc6a3f6648404ca4b99628add02ce86c2c2d0053296c7e23bea43b238d1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1176,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786500799</t>
+          <t>1786506510</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1186,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>38.390028</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1203,12 +1187,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x3efe4e02ea3d9bfa26256cae2117b7deedc84fd159b4045c452040d9b1f2d7c5</t>
+          <t>0x225af37bd68784b667dd9090dddf175f46682b7944262e33763cefe0142cf1a7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1218,22 +1202,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>160.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.1987</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1258,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1288,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786500797</t>
+          <t>1786506510</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1298,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>805.534591</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1315,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xbc8939d03f5d2c19550a7b112bffcf5adc6d07378d6ceb670253bc89f48240b6</t>
+          <t>0xcc22f26bdb2bbc6ad9d7a95a38487094355a81754e968974cf3207f8338c61fe</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1323,19 +1307,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>187.21</t>
+          <t>11.86614</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.4425</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1343,11 +1323,7 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1400,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786500775</t>
+          <t>1786506509</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1410,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>336.557303</t>
+          <t>26.816136</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1427,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9aab0146566e1cf2d904cec61e5fc8853c9b003f5b9a0f3c4e69d5d5b5c484ed</t>
+          <t>0x38bce125b4a0ba26f0e995d823c4eff0ff83796c863bd7add4577ce57da80549</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1435,31 +1411,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>63.35999</t>
+          <t>28.93346</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.5863</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1482,7 +1450,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1512,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786500773</t>
+          <t>1786506509</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1522,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>113.9056</t>
+          <t>49.35345</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1539,39 +1507,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xf93ca08ba4c183f19691ac949364bf8e7941471d36502742e2371e46518e091f</t>
+          <t>0x3a9b76743232f327ad980b41207f02851280ff9e55126e07c03237b84da0909e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>141.25895</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.2637</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1594,7 +1554,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1624,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786500761</t>
+          <t>1786506508</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1634,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>535.578957</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1651,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x81f5973a3f28d7aaeefe7911ffccf1e98af44fcaa930aeac34875dd38df71bc9</t>
+          <t>0x748826bf98c7e06abdf106bb54bb4f92c70058b63cc49ea45aa7a194035b9f9e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1666,22 +1626,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Paris Saint Germain -1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1706,7 +1666,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1736,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786500760</t>
+          <t>1786506475</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1746,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>47.388764</t>
+          <t>49.139466</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1763,12 +1723,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x66eeaf3004065d2e62328224d064e8196d58379f132fedbd741c76858295a7f7</t>
+          <t>0x4fe65d855d654462785a9c5f6aa2efeba944059d34dfe3176824b06bfab6f419</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1778,22 +1738,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>34.25998</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.6975</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1818,7 +1778,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0xdd50529e314a3663ff38eb9f9e48f9de046ea1f95c648f0b933df82946e0f1e0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1848,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786500757</t>
+          <t>1786506475</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1858,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>49.118251</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1875,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xbad5215a4edd54d38386bd1e5448631e76e90dbee3e4bf3557e8e2c043083418</t>
+          <t>0x14f0ae393ee20f24ac7e753e1048a908116153a8be11f5ffdf50c845267a6109</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1890,12 +1850,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>104.21999</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.5625</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1960,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786500752</t>
+          <t>1786506475</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1970,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>187.36178</t>
+          <t>49.493333</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1987,39 +1947,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xdd309ef6c0dc57692dec182e5cffcdd0c7f85c99189249002a5ee7c4793563d9</t>
+          <t>0xa662f283332f844a3d4ed39258ca689bfd404d00b13090d1f3709dfe24e922fd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>83.09999</t>
+          <t>3.47997</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.8075</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2042,7 +1994,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2072,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786500737</t>
+          <t>1786505944</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2082,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>149.39324</t>
+          <t>4.30956</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2099,39 +2051,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x96136c19e8b4b3c1cd9a022ec3ec1be7af2fc0def6358940a3b219bccf20682d</t>
+          <t>0x2327ae8911b0ecc308e6d44fdd634a294df35dd220e34dae08432da5c5591ea5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.4425</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2154,7 +2098,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2184,7 +2128,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786500736</t>
+          <t>1786504569</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2194,7 +2138,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>84.87191</t>
+          <t>2.259887</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2211,31 +2155,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x7b50006545a4d3976ffc8f0762f94bd9fdff1567a3cf664dd9e79edf834c96bc</t>
+          <t>0x96b610f32d9795f8cbb60a70db759bf5c6e8e8bda2b4112f2f4f89d76f146110</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>197.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.5312</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2258,7 +2210,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2288,7 +2240,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786500644</t>
+          <t>1786504435</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2298,7 +2250,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>444.382022</t>
+          <t>4.724706</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2315,28 +2267,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xf9e921304b5613d4f5a4aac94cdaeac732d8ea42bec44a92191306c7103df732</t>
+          <t>0x3e38be9d0b6d0fa3d03d49d262b9e0803a053310887577ce87e3581fea82ac7d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>369.91</t>
+          <t>252.25081</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2362,7 +2314,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2392,7 +2344,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786500633</t>
+          <t>1786504149</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2402,7 +2354,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>831.258427</t>
+          <t>528.273948</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2419,39 +2371,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xdf4ba60566fd5689393750a08058e1a227b21e0bb2b7a75524dd08921158b328</t>
+          <t>0x4aff54745ee1df9c39e5ceebddd57e339319f03a3082765f5bea3471c3a2fc6f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>690</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2474,7 +2418,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2504,7 +2448,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786500582</t>
+          <t>1786503841</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2514,7 +2458,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>1550.561798</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2531,12 +2475,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x5e90c46cc93882168350f5e6b83523a3325a59dffb9497b35253b8552791e3ab</t>
+          <t>0xd780d195ce364dd621ce45379699b2c7994680570e51d0eca2c1ed1143572b62</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2546,7 +2490,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1335.26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2616,7 +2560,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786500580</t>
+          <t>1786501059</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2626,7 +2570,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>2400.467416</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2643,12 +2587,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xa18586bdb3003365505e403bdf79edab1b8478a9e9e230f70c4e76fdf6d003cc</t>
+          <t>0x552df581fa9ee8db3d9033f3b2aae0d7a8a7e68bee7632a0f109eb9c8b3b8551</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2658,7 +2602,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2728,7 +2672,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786500551</t>
+          <t>1786500980</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2738,7 +2682,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>89.510112</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2755,7 +2699,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xcee60a04b8f8d5efba6d52111a13199c73c69fd54b9f9f9ba72592c359f92c6a</t>
+          <t>0x135ca5b241b0d1e484c97d7c26d71e9d58e6dd971b22360ae9e62df23118ee6b</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2770,7 +2714,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2840,7 +2784,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786500550</t>
+          <t>1786500974</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2850,7 +2794,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>49.078652</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2867,7 +2811,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x0909a65a14fd4ad7dbd184945e4e82c9fdce475552b31ac2ffa79f5cc8d2d2fc</t>
+          <t>0xd0e485c8a54ff92288008fc7ef998bfee28e3c9deabfed91f9266b54b7325639</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2952,7 +2896,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786500544</t>
+          <t>1786500803</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2979,12 +2923,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xf47ded4743419e912443bb01778bf84bf92c70cb548340b8471b4e65e69d5d72</t>
+          <t>0x32f75f1a679cbf6e5a754001684967d29f8331ea42c38c104d263619cd26bc14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2994,7 +2938,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3064,7 +3008,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786500534</t>
+          <t>1786500801</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3074,7 +3018,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>51.379775</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3091,7 +3035,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x944f5df4e4d993386c3114a59ad8704373224aae960b40c8fb5dc958868cd0c9</t>
+          <t>0xa4d6707462e7e71482a034711a024006ce64ad33f684e3ffc8aa48e105b8ad86</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3176,7 +3120,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786500504</t>
+          <t>1786500799</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3203,7 +3147,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x4ffb70fc7ea797009babeaf3a2360c329a379a328dab0ce16fa709514d4f9cef</t>
+          <t>0x3efe4e02ea3d9bfa26256cae2117b7deedc84fd159b4045c452040d9b1f2d7c5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3288,7 +3232,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786500503</t>
+          <t>1786500797</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3315,12 +3259,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x5c7eb9a2501c32b896b5a9b685517d32cbfe67726fca300d63b10476842d2c2a</t>
+          <t>0xbc8939d03f5d2c19550a7b112bffcf5adc6d07378d6ceb670253bc89f48240b6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3330,7 +3274,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>187.21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3400,7 +3344,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786500501</t>
+          <t>1786500775</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3410,7 +3354,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>336.557303</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3427,12 +3371,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x95e9e1a3038ffc59cdb49a206e8adcb19179a43073a098619bdd395c0570cb37</t>
+          <t>0x9aab0146566e1cf2d904cec61e5fc8853c9b003f5b9a0f3c4e69d5d5b5c484ed</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3442,7 +3386,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>63.35999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3512,7 +3456,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786500499</t>
+          <t>1786500773</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3522,7 +3466,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>113.9056</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3539,7 +3483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x0d5cd46de2f58ac252c6a0489b2fb8253629014f2f6b91d710ba41e1803b36b8</t>
+          <t>0xf93ca08ba4c183f19691ac949364bf8e7941471d36502742e2371e46518e091f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3624,7 +3568,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786500498</t>
+          <t>1786500761</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3651,12 +3595,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x5294d64dc44b1c637243f3de9a061ba385cc84408b2ea0a98d2ddf6c6718815c</t>
+          <t>0x81f5973a3f28d7aaeefe7911ffccf1e98af44fcaa930aeac34875dd38df71bc9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3666,7 +3610,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786500496</t>
+          <t>1786500760</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3746,7 +3690,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>47.388764</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3763,7 +3707,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xb5ce2ecec5f0be7b0047ce88d13d0c9055b5fca8d9c11bc67e966280f2384598</t>
+          <t>0x66eeaf3004065d2e62328224d064e8196d58379f132fedbd741c76858295a7f7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3848,7 +3792,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786500494</t>
+          <t>1786500757</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3875,12 +3819,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x7c3b5079c34701a023626323d701dfc0a4e7823959dc0481793b08574dc9dfd1</t>
+          <t>0xbad5215a4edd54d38386bd1e5448631e76e90dbee3e4bf3557e8e2c043083418</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3890,7 +3834,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>104.21999</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3960,7 +3904,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786500492</t>
+          <t>1786500752</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3970,7 +3914,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>187.36178</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3987,12 +3931,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xc25d80f3f8534bd014aa3041b4ded1b98e2b6f01f0f432a007e92f8d97721feb</t>
+          <t>0xdd309ef6c0dc57692dec182e5cffcdd0c7f85c99189249002a5ee7c4793563d9</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4002,7 +3946,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>83.09999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4072,7 +4016,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786500491</t>
+          <t>1786500737</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4082,7 +4026,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>149.39324</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4099,7 +4043,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x4b0fefa802aee78ae049407556ceab6fc43dd1967b5944a825593c40843bea6d</t>
+          <t>0x96136c19e8b4b3c1cd9a022ec3ec1be7af2fc0def6358940a3b219bccf20682d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4114,7 +4058,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>47.21</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4184,7 +4128,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786500476</t>
+          <t>1786500736</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4194,7 +4138,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>66.570787</t>
+          <t>84.87191</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4211,27 +4155,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x8e07b84ce6844c38bd99c9ded59e55289f96bab45374d6cafd8039a6848c3ae1</t>
+          <t>0x7b50006545a4d3976ffc8f0762f94bd9fdff1567a3cf664dd9e79edf834c96bc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>132.26</t>
+          <t>197.75</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4239,11 +4179,7 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4296,7 +4232,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786500474</t>
+          <t>1786500644</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4306,7 +4242,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>237.770787</t>
+          <t>444.382022</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4323,27 +4259,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x0aea6283317d83074694b78f764d29c7b95d51f4e307b7019541bd6400e1a8b8</t>
+          <t>0xf9e921304b5613d4f5a4aac94cdaeac732d8ea42bec44a92191306c7103df732</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>76.86</t>
+          <t>369.91</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4351,11 +4283,7 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4408,7 +4336,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786500468</t>
+          <t>1786500633</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4418,7 +4346,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>138.175281</t>
+          <t>831.258427</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4435,12 +4363,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xdda980bbea51d427848750fa29aa6f27e23db79e2c7c5629a9587f9bde755ba9</t>
+          <t>0xdf4ba60566fd5689393750a08058e1a227b21e0bb2b7a75524dd08921158b328</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4450,7 +4378,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>77.35999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4520,7 +4448,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786500460</t>
+          <t>1786500582</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4530,7 +4458,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>139.074139</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4547,12 +4475,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xe29c36778555e41d28b19553e722e94874412123ccb1bedea115d69ba68e5e12</t>
+          <t>0x5e90c46cc93882168350f5e6b83523a3325a59dffb9497b35253b8552791e3ab</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4562,7 +4490,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>41.10999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4632,7 +4560,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786500458</t>
+          <t>1786500580</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4642,7 +4570,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>73.9056</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4659,7 +4587,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x29146d1a0dbde03d831d263bc99690b03cefcdfa8dc20dedd782669d6c9213f9</t>
+          <t>0xa18586bdb3003365505e403bdf79edab1b8478a9e9e230f70c4e76fdf6d003cc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4674,7 +4602,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>120.74</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4744,7 +4672,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786500456</t>
+          <t>1786500551</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4754,7 +4682,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>217.060674</t>
+          <t>89.510112</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4771,7 +4699,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x7bc5af8f4863cacf664ab30c084a2a43acfbcc9eff568595a2106ce23da17209</t>
+          <t>0xcee60a04b8f8d5efba6d52111a13199c73c69fd54b9f9f9ba72592c359f92c6a</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4786,7 +4714,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4856,7 +4784,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786500454</t>
+          <t>1786500550</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4866,7 +4794,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>49.222472</t>
+          <t>49.078652</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4883,12 +4811,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x5ae0620d3e7fd0d39c61c92d92dff0f44ffb8e289337ebe156f3686d570026cf</t>
+          <t>0x0909a65a14fd4ad7dbd184945e4e82c9fdce475552b31ac2ffa79f5cc8d2d2fc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4898,7 +4826,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>114.08</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4968,7 +4896,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786500453</t>
+          <t>1786500544</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4978,7 +4906,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>205.08764</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4995,7 +4923,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xf59e1f15c89fd009ceb1441f549470bd61d335d24c57df7a653f34a3fed23904</t>
+          <t>0xf47ded4743419e912443bb01778bf84bf92c70cb548340b8471b4e65e69d5d72</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5010,7 +4938,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>28.58</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5080,7 +5008,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786500452</t>
+          <t>1786500534</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5090,7 +5018,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>75.595506</t>
+          <t>51.379775</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5107,12 +5035,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x7d734049fc9657458d52a381d19fb7d4aff8c4e71148efedd691e610e3a7a0bb</t>
+          <t>0x944f5df4e4d993386c3114a59ad8704373224aae960b40c8fb5dc958868cd0c9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5122,7 +5050,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1005.29</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5192,7 +5120,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786500451</t>
+          <t>1786500504</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5202,7 +5130,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1807.262921</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5219,12 +5147,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xdac326f5927fbb970e6253d4f41b0dda53f675cb5449d4ce88a3392cdb3f18d2</t>
+          <t>0x4ffb70fc7ea797009babeaf3a2360c329a379a328dab0ce16fa709514d4f9cef</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5234,22 +5162,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.3975</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5274,7 +5202,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5304,7 +5232,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786499763</t>
+          <t>1786500503</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5314,7 +5242,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>49.207547</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5331,36 +5259,44 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xe4d62db20d7dce5a6d3aba1b5840a8cfadcc44c5e125c97cb74db1289ff05051</t>
+          <t>0x5c7eb9a2501c32b896b5a9b685517d32cbfe67726fca300d63b10476842d2c2a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -5378,7 +5314,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x79833fc6a3f6648404ca4b99628add02ce86c2c2d0053296c7e23bea43b238d1</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5408,7 +5344,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786498202</t>
+          <t>1786500501</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5418,7 +5354,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>21.408451</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5435,12 +5371,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x7dcf5f848d78758aa81a9026f7a2af5c72cc084687859ec7c1750f509bdc420b</t>
+          <t>0x95e9e1a3038ffc59cdb49a206e8adcb19179a43073a098619bdd395c0570cb37</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5450,39 +5386,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -5490,7 +5426,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5520,7 +5456,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786496166</t>
+          <t>1786500499</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5530,7 +5466,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>10.511211</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5547,12 +5483,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x42cfdc40991be588eb224c94dbbda3512b84f29d8a76e0e819f1717e16ea7f3a</t>
+          <t>0x0d5cd46de2f58ac252c6a0489b2fb8253629014f2f6b91d710ba41e1803b36b8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5562,22 +5498,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5602,7 +5538,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5632,7 +5568,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786496166</t>
+          <t>1786500498</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5642,7 +5578,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>49.348946</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5659,23 +5595,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xfafaa95fa892b7b96feb25237a96968c1542b373c172067c131656aed4764872</t>
+          <t>0x5294d64dc44b1c637243f3de9a061ba385cc84408b2ea0a98d2ddf6c6718815c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>22.08887</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5683,7 +5623,11 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5736,7 +5680,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786495559</t>
+          <t>1786500496</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5746,7 +5690,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>49.498868</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5763,31 +5707,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x2e1abfbad55d92ecb1113f9023da45bba5096910055bdcd79fd58fee8ad506ef</t>
+          <t>0xb5ce2ecec5f0be7b0047ce88d13d0c9055b5fca8d9c11bc67e966280f2384598</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>14.82799</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5810,7 +5762,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5840,7 +5792,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786495559</t>
+          <t>1786500494</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5850,7 +5802,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>33.227989</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5867,12 +5819,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xda319e704a52e8ad3239c54f090757c46923aed8a6229dbb1a47a6aafdacc178</t>
+          <t>0x7c3b5079c34701a023626323d701dfc0a4e7823959dc0481793b08574dc9dfd1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5882,12 +5834,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1.14999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5952,7 +5904,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786494130</t>
+          <t>1786500492</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5962,7 +5914,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2.04898</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5979,12 +5931,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xe8544bdaf431d2b9cded859bb44c95e9a4cbb77d283569ab427748adf7c38a82</t>
+          <t>0xc25d80f3f8534bd014aa3041b4ded1b98e2b6f01f0f432a007e92f8d97721feb</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5994,39 +5946,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -6034,7 +5986,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -6064,7 +6016,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786494129</t>
+          <t>1786500491</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -6074,7 +6026,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>8.232143</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6091,12 +6043,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x9f99840ce6a1d8f4c6f24f53d1e8ba96ef427cfa8f43a387601bdf53f416e3a4</t>
+          <t>0x4b0fefa802aee78ae049407556ceab6fc43dd1967b5944a825593c40843bea6d</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6106,12 +6058,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6176,7 +6128,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786494097</t>
+          <t>1786500476</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6186,7 +6138,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>66.570787</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6203,12 +6155,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x17444d1a79b59787a6df8c716bc91f6b83490b852e7a42e1da13278178bd0fa3</t>
+          <t>0x8e07b84ce6844c38bd99c9ded59e55289f96bab45374d6cafd8039a6848c3ae1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6218,39 +6170,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>132.26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -6258,7 +6210,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6288,7 +6240,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786494077</t>
+          <t>1786500474</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6298,7 +6250,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>28.986547</t>
+          <t>237.770787</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6315,12 +6267,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xed62cce657564c54cdf4505d1beb541e7bb3559d7e8dafcf5c91e22df2dab644</t>
+          <t>0x0aea6283317d83074694b78f764d29c7b95d51f4e307b7019541bd6400e1a8b8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6330,22 +6282,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>76.86</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6370,7 +6322,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6400,7 +6352,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786494054</t>
+          <t>1786500468</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6410,7 +6362,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>58.54359</t>
+          <t>138.175281</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6427,7 +6379,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x5e9b92a3ee864ed306ae19b1eb8415371da432df1801adf9df4096158c2ada97</t>
+          <t>0xdda980bbea51d427848750fa29aa6f27e23db79e2c7c5629a9587f9bde755ba9</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6435,15 +6387,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22.15226</t>
+          <t>77.35999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6451,7 +6407,11 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -6504,7 +6464,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786491019</t>
+          <t>1786500460</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6514,7 +6474,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>49.502257</t>
+          <t>139.074139</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6531,12 +6491,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x23733dbdf9fa3729981e360673c4b7d7c10ff2531e371c5badad3796d6c9c512</t>
+          <t>0xe29c36778555e41d28b19553e722e94874412123ccb1bedea115d69ba68e5e12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6546,12 +6506,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>27.55999</t>
+          <t>41.10999</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6616,7 +6576,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786490560</t>
+          <t>1786500458</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6626,7 +6586,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>49.43496</t>
+          <t>73.9056</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6643,7 +6603,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x0727088f0a4a30c10d202e7c81d28be4eb0ab98bf21e981e558f2e5179605bac</t>
+          <t>0x29146d1a0dbde03d831d263bc99690b03cefcdfa8dc20dedd782669d6c9213f9</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6651,23 +6611,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15.81921</t>
+          <t>120.74</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -6690,7 +6658,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6720,7 +6688,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786490214</t>
+          <t>1786500456</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6730,7 +6698,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>35.44921</t>
+          <t>217.060674</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6747,12 +6715,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x2e03fcc3f7ecc087552ed1d69a1f8008e36e398bfe42ea205ce282f08f1c1340</t>
+          <t>0x7bc5af8f4863cacf664ab30c084a2a43acfbcc9eff568595a2106ce23da17209</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6762,7 +6730,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>13.87999</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6772,29 +6740,29 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -6802,7 +6770,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6832,7 +6800,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786490114</t>
+          <t>1786500454</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6842,7 +6810,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>24.952791</t>
+          <t>49.222472</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6859,7 +6827,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x031e42fbfd08a3c7d769259edbc4291e998075aee0ff949b46b2ff5a320f4fb9</t>
+          <t>0x5ae0620d3e7fd0d39c61c92d92dff0f44ffb8e289337ebe156f3686d570026cf</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6874,22 +6842,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>114.08</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6914,7 +6882,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6944,7 +6912,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786487872</t>
+          <t>1786500453</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6954,7 +6922,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>3.62449</t>
+          <t>205.08764</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6971,12 +6939,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x973ce82e34197c696686774e4b32dc293666e3b1f344b3c042ea8e0bc0baf472</t>
+          <t>0xf59e1f15c89fd009ceb1441f549470bd61d335d24c57df7a653f34a3fed23904</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6986,22 +6954,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.2463</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7026,7 +6994,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -7056,7 +7024,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786484906</t>
+          <t>1786500452</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -7066,7 +7034,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>12.182741</t>
+          <t>75.595506</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7083,12 +7051,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x4189c1704e3efda1c32f863bee5edac536cbbc1ddc5c7ff92ffcec3f8671f4dd</t>
+          <t>0x7d734049fc9657458d52a381d19fb7d4aff8c4e71148efedd691e610e3a7a0bb</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -7098,22 +7066,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1005.29</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7138,7 +7106,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -7168,7 +7136,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786483830</t>
+          <t>1786500451</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7178,7 +7146,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>9.433962</t>
+          <t>1807.262921</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7195,12 +7163,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x86035074a77352f25945be3c07a1ce0a72476812a4d9ee7a5d31accc0005ca8e</t>
+          <t>0xdac326f5927fbb970e6253d4f41b0dda53f675cb5449d4ce88a3392cdb3f18d2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7210,22 +7178,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.14549</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.3975</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7250,7 +7218,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7280,7 +7248,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786483821</t>
+          <t>1786499763</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7290,7 +7258,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>4.06728</t>
+          <t>49.207547</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7307,28 +7275,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x95d1a72bec5f6cbef6a0bee578fc49d11315543f98d64986bc30ab10b98ab235</t>
+          <t>0xe4d62db20d7dce5a6d3aba1b5840a8cfadcc44c5e125c97cb74db1289ff05051</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.6987</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>UEFA Super Cup</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -7354,7 +7322,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
+          <t>0x79833fc6a3f6648404ca4b99628add02ce86c2c2d0053296c7e23bea43b238d1</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7384,7 +7352,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786481014</t>
+          <t>1786498202</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7394,7 +7362,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>429.338104</t>
+          <t>21.408451</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7411,7 +7379,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x75abf2cc9245d94d8697557465991a972b17d428172f9c86e5103ccf4513ae1d</t>
+          <t>0x7dcf5f848d78758aa81a9026f7a2af5c72cc084687859ec7c1750f509bdc420b</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7419,23 +7387,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>280.65999</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -7458,7 +7434,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7488,7 +7464,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786479821</t>
+          <t>1786496166</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7498,7 +7474,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>400.942843</t>
+          <t>10.511211</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7515,12 +7491,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x7b6931100ecd01485a88a37e39d7604129b6c1b4774ef01d18474422b8022991</t>
+          <t>0x42cfdc40991be588eb224c94dbbda3512b84f29d8a76e0e819f1717e16ea7f3a</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -7530,22 +7506,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>295.34</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7570,7 +7546,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7600,7 +7576,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786479008</t>
+          <t>1786496166</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7610,7 +7586,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1211.651282</t>
+          <t>49.348946</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7627,28 +7603,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xfd5730799b860d55deb75e792b32577fe97b21a6872bcdcae76b7d727aa3f5e1</t>
+          <t>0xfafaa95fa892b7b96feb25237a96968c1542b373c172067c131656aed4764872</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>15.78675</t>
+          <t>22.08887</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7674,7 +7650,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7704,7 +7680,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786478908</t>
+          <t>1786495559</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7714,7 +7690,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>35.475843</t>
+          <t>49.498868</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7731,23 +7707,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xaa6b20356dec3ef3de3c3740df5cda0bfaf51ac484d1b2f78d6d001ebf63c609</t>
+          <t>0x2e1abfbad55d92ecb1113f9023da45bba5096910055bdcd79fd58fee8ad506ef</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>0.00327</t>
+          <t>14.82799</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.7675</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7778,7 +7754,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7808,7 +7784,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786478826</t>
+          <t>1786495559</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7818,7 +7794,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>0.004261</t>
+          <t>33.227989</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7835,12 +7811,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x1ca2c2e3faa5fd0586c76f29023f0ae32e5b7eb91a5e924bff0c79c1fd8e3978</t>
+          <t>0xda319e704a52e8ad3239c54f090757c46923aed8a6229dbb1a47a6aafdacc178</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -7850,22 +7826,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>1.14999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7890,7 +7866,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7920,7 +7896,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786478809</t>
+          <t>1786494130</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7930,7 +7906,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>31.220513</t>
+          <t>2.04898</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7947,7 +7923,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xd719c5ae636d9e747b1caa23c9df7ac916d22589ebafce09e6a90f528305ad43</t>
+          <t>0xe8544bdaf431d2b9cded859bb44c95e9a4cbb77d283569ab427748adf7c38a82</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7955,15 +7931,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7971,7 +7951,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -7994,7 +7978,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8024,7 +8008,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786478807</t>
+          <t>1786494129</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -8034,7 +8018,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>39.736842</t>
+          <t>8.232143</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -8051,12 +8035,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x7e152d80b0c185c0abe8c4ca426947b4261d81003670d3822de824587a968e1d</t>
+          <t>0x9f99840ce6a1d8f4c6f24f53d1e8ba96ef427cfa8f43a387601bdf53f416e3a4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8066,12 +8050,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.5637</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -8136,7 +8120,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786478806</t>
+          <t>1786494097</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8146,7 +8130,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>49.507761</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8163,12 +8147,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x762726fa569798e9bb38e6d1d3a6718a3e6b17854ec943996f440407d07d5af1</t>
+          <t>0x17444d1a79b59787a6df8c716bc91f6b83490b852e7a42e1da13278178bd0fa3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8178,12 +8162,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>30.51955</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -8193,32 +8177,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8248,7 +8232,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786478801</t>
+          <t>1786494077</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8258,7 +8242,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>148.875854</t>
+          <t>28.986547</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8275,12 +8259,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x8e47fef69d97d7a182f242c2cdce1afab730128f4310cd28a6f9c5d37adae0d1</t>
+          <t>0xed62cce657564c54cdf4505d1beb541e7bb3559d7e8dafcf5c91e22df2dab644</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8290,12 +8274,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>36.47459</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -8360,7 +8344,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786478798</t>
+          <t>1786494054</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8370,7 +8354,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>148.875878</t>
+          <t>58.54359</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8387,28 +8371,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x4b13bf02996be9f8f2f945b0a566bfd6a4a430bd57ac43a76f92d64f15f5498d</t>
+          <t>0x5e9b92a3ee864ed306ae19b1eb8415371da432df1801adf9df4096158c2ada97</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>66.06366</t>
+          <t>22.15226</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8434,7 +8418,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8464,7 +8448,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786478774</t>
+          <t>1786491019</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8474,7 +8458,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>148.875854</t>
+          <t>49.502257</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8491,31 +8475,39 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xe9e3237227be288d77eb896c110ca16fd4018525f8bcea0d1e30930f9032da8b</t>
+          <t>0x23733dbdf9fa3729981e360673c4b7d7c10ff2531e371c5badad3796d6c9c512</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2.10999</t>
+          <t>27.55999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -8538,7 +8530,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -8568,7 +8560,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786478768</t>
+          <t>1786490560</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8578,7 +8570,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>2.776303</t>
+          <t>49.43496</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8595,27 +8587,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x4c9eb0ce8768b1300644ee9d6d756f3477ae0a67da7b2d98350ea8c35a646255</t>
+          <t>0x0727088f0a4a30c10d202e7c81d28be4eb0ab98bf21e981e558f2e5179605bac</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>15.81921</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8623,26 +8611,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -8680,7 +8664,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786478575</t>
+          <t>1786490214</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8690,7 +8674,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>23.786192</t>
+          <t>35.44921</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8707,23 +8691,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x3991dd65a93f5a305e8899432f4bb1612f1b874d3aa09a9a9266778002ba1f22</t>
+          <t>0x2e03fcc3f7ecc087552ed1d69a1f8008e36e398bfe42ea205ce282f08f1c1340</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>280.97998</t>
+          <t>13.87999</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8731,7 +8719,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -8754,7 +8746,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8784,7 +8776,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786478575</t>
+          <t>1786490114</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8794,7 +8786,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>369.7105</t>
+          <t>24.952791</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8811,12 +8803,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
+          <t>0x031e42fbfd08a3c7d769259edbc4291e998075aee0ff949b46b2ff5a320f4fb9</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8826,22 +8818,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8866,7 +8858,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8896,7 +8888,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786477844</t>
+          <t>1786487872</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8906,7 +8898,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>44.882051</t>
+          <t>3.62449</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8923,23 +8915,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
+          <t>0x973ce82e34197c696686774e4b32dc293666e3b1f344b3c042ea8e0bc0baf472</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.2463</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8947,7 +8943,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786477225</t>
+          <t>1786484906</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>6016.713092</t>
+          <t>12.182741</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9027,31 +9027,39 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
+          <t>0x4189c1704e3efda1c32f863bee5edac536cbbc1ddc5c7ff92ffcec3f8671f4dd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>688.37615</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -9074,7 +9082,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9104,7 +9112,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786476767</t>
+          <t>1786483830</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9114,7 +9122,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1533.98585</t>
+          <t>9.433962</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9131,12 +9139,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
+          <t>0x86035074a77352f25945be3c07a1ce0a72476812a4d9ee7a5d31accc0005ca8e</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9146,22 +9154,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.14549</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9186,7 +9194,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9216,7 +9224,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786476263</t>
+          <t>1786483821</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9226,7 +9234,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>73.723077</t>
+          <t>4.06728</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9243,39 +9251,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
+          <t>0x95d1a72bec5f6cbef6a0bee578fc49d11315543f98d64986bc30ab10b98ab235</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.3075</t>
+          <t>1.6987</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
+          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786473059</t>
+          <t>1786481014</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>15.447154</t>
+          <t>429.338104</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9355,28 +9355,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
+          <t>0x75abf2cc9245d94d8697557465991a972b17d428172f9c86e5103ccf4513ae1d</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>280.65999</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
+          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786466862</t>
+          <t>1786479821</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>586.482759</t>
+          <t>400.942843</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9459,7 +9459,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
+          <t>0x7b6931100ecd01485a88a37e39d7604129b6c1b4774ef01d18474422b8022991</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9467,23 +9467,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>295.34</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -9506,7 +9514,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9536,7 +9544,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786466015</t>
+          <t>1786479008</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9546,7 +9554,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>16.675105</t>
+          <t>1211.651282</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9563,39 +9571,31 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
+          <t>0xfd5730799b860d55deb75e792b32577fe97b21a6872bcdcae76b7d727aa3f5e1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>119.23</t>
+          <t>15.78675</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786465613</t>
+          <t>1786478908</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>662.388889</t>
+          <t>35.475843</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9675,23 +9675,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
+          <t>0xaa6b20356dec3ef3de3c3740df5cda0bfaf51ac484d1b2f78d6d001ebf63c609</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>0.00327</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.7675</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786462484</t>
+          <t>1786478826</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>24.911111</t>
+          <t>0.004261</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9779,12 +9779,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
+          <t>0x1ca2c2e3faa5fd0586c76f29023f0ae32e5b7eb91a5e924bff0c79c1fd8e3978</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>23.9188</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9809,32 +9809,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786460921</t>
+          <t>1786478809</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>111.250233</t>
+          <t>31.220513</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9891,28 +9891,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
+          <t>0xd719c5ae636d9e747b1caa23c9df7ac916d22589ebafce09e6a90f528305ad43</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786459823</t>
+          <t>1786478807</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>3.232323</t>
+          <t>39.736842</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9995,31 +9995,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
+          <t>0x7e152d80b0c185c0abe8c4ca426947b4261d81003670d3822de824587a968e1d</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.5637</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10042,7 +10050,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -10072,7 +10080,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786459704</t>
+          <t>1786478806</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -10082,7 +10090,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>343.089431</t>
+          <t>49.507761</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10099,31 +10107,39 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
+          <t>0x762726fa569798e9bb38e6d1d3a6718a3e6b17854ec943996f440407d07d5af1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>280.99999</t>
+          <t>30.51955</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10146,7 +10162,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10176,7 +10192,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786459347</t>
+          <t>1786478801</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10186,7 +10202,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>456.910553</t>
+          <t>148.875854</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10203,31 +10219,39 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
+          <t>0x8e47fef69d97d7a182f242c2cdce1afab730128f4310cd28a6f9c5d37adae0d1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>312.25</t>
+          <t>36.47459</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.245</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10250,7 +10274,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10280,7 +10304,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1786431942</t>
+          <t>1786478798</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10290,7 +10314,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>647.150259</t>
+          <t>148.875878</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10307,27 +10331,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+          <t>0x4b13bf02996be9f8f2f945b0a566bfd6a4a430bd57ac43a76f92d64f15f5498d</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>6.00999</t>
+          <t>66.06366</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10335,26 +10355,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K91" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -10392,7 +10408,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1786424623</t>
+          <t>1786478774</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10402,7 +10418,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>10.977151</t>
+          <t>148.875854</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10419,28 +10435,28 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+          <t>0xe9e3237227be288d77eb896c110ca16fd4018525f8bcea0d1e30930f9032da8b</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.10999</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -10466,7 +10482,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -10496,7 +10512,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1786421953</t>
+          <t>1786478768</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10506,7 +10522,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>2.040816</t>
+          <t>2.776303</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10523,31 +10539,39 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+          <t>0x4c9eb0ce8768b1300644ee9d6d756f3477ae0a67da7b2d98350ea8c35a646255</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10570,7 +10594,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10600,7 +10624,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1786421917</t>
+          <t>1786478575</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10610,7 +10634,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>138.77551</t>
+          <t>23.786192</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10627,28 +10651,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+          <t>0x3991dd65a93f5a305e8899432f4bb1612f1b874d3aa09a9a9266778002ba1f22</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>280.97998</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -10674,7 +10698,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10704,7 +10728,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1786421886</t>
+          <t>1786478575</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10714,7 +10738,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>18.414322</t>
+          <t>369.7105</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10731,31 +10755,39 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10778,7 +10810,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10808,7 +10840,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786477844</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10818,7 +10850,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>44.882051</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10835,39 +10867,31 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10890,7 +10914,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10920,7 +10944,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786477225</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10930,7 +10954,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>6016.713092</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10947,39 +10971,31 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>688.37615</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -11002,7 +11018,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -11032,7 +11048,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786476767</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -11042,7 +11058,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>1533.98585</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -11059,7 +11075,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -11074,12 +11090,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -11089,24 +11105,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K98" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -11114,7 +11130,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -11144,7 +11160,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786476263</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -11154,7 +11170,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>73.723077</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11171,12 +11187,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11186,47 +11202,47 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.3075</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -11256,7 +11272,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786473059</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11266,7 +11282,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>15.447154</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11283,28 +11299,28 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -11330,7 +11346,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -11360,7 +11376,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786466862</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11370,7 +11386,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>586.482759</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11387,28 +11403,28 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -11434,7 +11450,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -11464,7 +11480,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786466015</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11474,7 +11490,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>16.675105</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11491,31 +11507,39 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>119.23</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -11538,7 +11562,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -11568,7 +11592,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786465613</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11578,7 +11602,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>662.388889</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11595,23 +11619,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11642,7 +11666,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -11672,7 +11696,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786462484</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11682,7 +11706,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>24.911111</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11699,12 +11723,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11714,22 +11738,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>23.9188</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11754,7 +11778,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -11784,7 +11808,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786460921</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11794,7 +11818,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>111.250233</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11811,39 +11835,31 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Over 1.5</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -11866,7 +11882,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -11896,7 +11912,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786459823</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11906,7 +11922,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>3.232323</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11923,39 +11939,31 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -11978,7 +11986,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -12008,7 +12016,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786459704</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -12018,7 +12026,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>343.089431</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -12035,28 +12043,28 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>280.99999</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>UEFA Super Cup</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -12082,7 +12090,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -12112,7 +12120,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786459347</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -12122,7 +12130,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>456.910553</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -12139,62 +12147,54 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>312.25</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.4825</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786431942</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>647.150259</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12251,110 +12251,2054 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>6.00999</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1.5475</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>1786424623</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>10.977151</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>1786421953</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>2.040816</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>1786421917</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>138.77551</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1.4888</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>1786421886</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>18.414322</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>216.99999</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1.4888</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>1786409895</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>443.989749</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>13.13154</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1.065</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>1786390904</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>202.023692</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>11.30985</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1.065</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>1786390902</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>173.997692</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>12.49</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1.5475</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>1786371203</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>22.812785</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1.2163</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>1786334647</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>13.872832</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>1786316612</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>1786316590</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>331.57222</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1.7988</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>1786316229</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>415.11389</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>20.70997</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>1786316213</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>26.009381</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>74.68</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>1786310047</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>206.726644</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>65.17485</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>1786309443</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>87.48302</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I127" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J127" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="K127" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
+      <c r="S127" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T109" t="inlineStr">
+      <c r="T127" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="U127" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr">
+      <c r="V127" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
+++ b/data/sxbet/ligas/UEFA Super Cup/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V127"/>
+  <dimension ref="A1:V133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x0927d4c3e3931cdf9a37f03c0814f362709f2c0054156bff909783124cd97ba4</t>
+          <t>0x14ad991d40ea7b0aea15b15d1403360e01e33cab725b1a6d4bc87ef41346d69f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,17 +542,17 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786507172</t>
+          <t>1786510838</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>79.692308</t>
+          <t>204.643678</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x9fddadee598b90df36d4beeaccd01cac540422762fccc11680d1a8c1c770bc25</t>
+          <t>0xcaf51c1ca3d7c8c1327c59fce8e02f85bc033633736c359d2fec4dee66db873a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +650,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.99999</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5637</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786506876</t>
+          <t>1786510835</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>5.62059</t>
+          <t>49.507761</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,39 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xeaededa5eb1eec58e3a92c47dc6cb4169278932bfd131653a2a27ffed2fee2cd</t>
+          <t>0x2ad0a1d2a5801c1ff0576548bfc9cbc375028aea76566bb9086e97296389cbaf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>81.46</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5637</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -802,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786506875</t>
+          <t>1786510835</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>49.507761</t>
+          <t>187.264368</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,12 +851,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x319d6fb0294ad8704b8abbe0d4e4c67f67b020f4d665c10e7219bac1dcba5ae9</t>
+          <t>0x97cdff71f0d83b9e703d7c7f41ab1662969e65623c0cadbe682dac21ec5721ad</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -874,39 +866,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7475</t>
+          <t>1.3987</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -914,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786506563</t>
+          <t>1786510834</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>28.508361</t>
+          <t>17.780564</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,39 +963,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x2a712e8cbf8e60615d12ed5c38e599dff972e67ca964e58797cc9a64951d583f</t>
+          <t>0x82eccf3a1cc1033f8898125853076c3372cde7a0d43a7691e3ddf4ec6479d138</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>57.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4225</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1026,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786506563</t>
+          <t>1786510675</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>44.87574</t>
+          <t>129.590909</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,28 +1067,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xade17fdc3c72bd54c67008038259583e24f46a47edddd5d0a65e7780edf4f60b</t>
+          <t>0xa7a3a693fd32680e781fc16d71693a38ddc3dd2c51d7c887ba35eaabb05a34fc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10.12537</t>
+          <t>27.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.0662</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UEFA Super Cup</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1130,7 +1114,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x79833fc6a3f6648404ca4b99628add02ce86c2c2d0053296c7e23bea43b238d1</t>
+          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786506510</t>
+          <t>1786508472</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>38.390028</t>
+          <t>421.584906</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,62 +1171,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x225af37bd68784b667dd9090dddf175f46682b7944262e33763cefe0142cf1a7</t>
+          <t>0x0927d4c3e3931cdf9a37f03c0814f362709f2c0054156bff909783124cd97ba4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>160.1</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.1987</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1248,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786506510</t>
+          <t>1786507172</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1258,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>805.534591</t>
+          <t>79.692308</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,31 +1275,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xcc22f26bdb2bbc6ad9d7a95a38487094355a81754e968974cf3207f8338c61fe</t>
+          <t>0x9fddadee598b90df36d4beeaccd01cac540422762fccc11680d1a8c1c770bc25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.86614</t>
+          <t>2.99999</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4425</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1346,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786506509</t>
+          <t>1786506876</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>26.816136</t>
+          <t>5.62059</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,31 +1387,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x38bce125b4a0ba26f0e995d823c4eff0ff83796c863bd7add4577ce57da80549</t>
+          <t>0xeaededa5eb1eec58e3a92c47dc6cb4169278932bfd131653a2a27ffed2fee2cd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28.93346</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5863</t>
+          <t>1.5637</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1450,7 +1442,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786506509</t>
+          <t>1786506875</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>49.35345</t>
+          <t>49.507761</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,23 +1499,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x3a9b76743232f327ad980b41207f02851280ff9e55126e07c03237b84da0909e</t>
+          <t>0x319d6fb0294ad8704b8abbe0d4e4c67f67b020f4d665c10e7219bac1dcba5ae9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>141.25895</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2637</t>
+          <t>1.7475</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1531,7 +1527,11 @@
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786506508</t>
+          <t>1786506563</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>535.578957</t>
+          <t>28.508361</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x748826bf98c7e06abdf106bb54bb4f92c70058b63cc49ea45aa7a194035b9f9e</t>
+          <t>0x2a712e8cbf8e60615d12ed5c38e599dff972e67ca964e58797cc9a64951d583f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1626,12 +1626,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>18.96</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.4225</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786506475</t>
+          <t>1786506563</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>49.139466</t>
+          <t>44.87574</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1723,39 +1723,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x4fe65d855d654462785a9c5f6aa2efeba944059d34dfe3176824b06bfab6f419</t>
+          <t>0xade17fdc3c72bd54c67008038259583e24f46a47edddd5d0a65e7780edf4f60b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>34.25998</t>
+          <t>10.12537</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6975</t>
+          <t>1.2637</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Over 2.0</t>
-        </is>
-      </c>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -1778,7 +1770,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xdd50529e314a3663ff38eb9f9e48f9de046ea1f95c648f0b933df82946e0f1e0</t>
+          <t>0x79833fc6a3f6648404ca4b99628add02ce86c2c2d0053296c7e23bea43b238d1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1800,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786506475</t>
+          <t>1786506510</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1810,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>49.118251</t>
+          <t>38.390028</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,7 +1827,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x14f0ae393ee20f24ac7e753e1048a908116153a8be11f5ffdf50c845267a6109</t>
+          <t>0x225af37bd68784b667dd9090dddf175f46682b7944262e33763cefe0142cf1a7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1850,22 +1842,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>160.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5625</t>
+          <t>1.1987</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1890,7 +1882,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1920,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786506475</t>
+          <t>1786506510</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1930,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>49.493333</t>
+          <t>805.534591</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,28 +1939,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xa662f283332f844a3d4ed39258ca689bfd404d00b13090d1f3709dfe24e922fd</t>
+          <t>0xcc22f26bdb2bbc6ad9d7a95a38487094355a81754e968974cf3207f8338c61fe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3.47997</t>
+          <t>11.86614</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.8075</t>
+          <t>1.4425</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1994,7 +1986,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2024,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786505944</t>
+          <t>1786506509</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2034,7 +2026,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4.30956</t>
+          <t>26.816136</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,28 +2043,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x2327ae8911b0ecc308e6d44fdd634a294df35dd220e34dae08432da5c5591ea5</t>
+          <t>0x38bce125b4a0ba26f0e995d823c4eff0ff83796c863bd7add4577ce57da80549</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28.93346</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4425</t>
+          <t>1.5863</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2098,7 +2090,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2128,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786504569</t>
+          <t>1786506509</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2130,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2.259887</t>
+          <t>49.35345</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,39 +2147,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x96b610f32d9795f8cbb60a70db759bf5c6e8e8bda2b4112f2f4f89d76f146110</t>
+          <t>0x3a9b76743232f327ad980b41207f02851280ff9e55126e07c03237b84da0909e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>141.25895</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5312</t>
+          <t>1.2637</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2210,7 +2194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2240,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786504435</t>
+          <t>1786506508</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2250,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4.724706</t>
+          <t>535.578957</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2267,31 +2251,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x3e38be9d0b6d0fa3d03d49d262b9e0803a053310887577ce87e3581fea82ac7d</t>
+          <t>0x748826bf98c7e06abdf106bb54bb4f92c70058b63cc49ea45aa7a194035b9f9e</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>252.25081</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4775</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -1</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2314,7 +2306,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2344,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786504149</t>
+          <t>1786506475</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2354,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>528.273948</t>
+          <t>49.139466</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,31 +2363,39 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x4aff54745ee1df9c39e5ceebddd57e339319f03a3082765f5bea3471c3a2fc6f</t>
+          <t>0x4fe65d855d654462785a9c5f6aa2efeba944059d34dfe3176824b06bfab6f419</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>34.25998</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.6975</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0xdd50529e314a3663ff38eb9f9e48f9de046ea1f95c648f0b933df82946e0f1e0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786503841</t>
+          <t>1786506475</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1550.561798</t>
+          <t>49.118251</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,7 +2475,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xd780d195ce364dd621ce45379699b2c7994680570e51d0eca2c1ed1143572b62</t>
+          <t>0x14f0ae393ee20f24ac7e753e1048a908116153a8be11f5ffdf50c845267a6109</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1335.26</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.5625</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786501059</t>
+          <t>1786506475</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2400.467416</t>
+          <t>49.493333</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2587,39 +2587,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x552df581fa9ee8db3d9033f3b2aae0d7a8a7e68bee7632a0f109eb9c8b3b8551</t>
+          <t>0xa662f283332f844a3d4ed39258ca689bfd404d00b13090d1f3709dfe24e922fd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3.47997</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.8075</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2642,7 +2634,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2672,7 +2664,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786500980</t>
+          <t>1786505944</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2682,7 +2674,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>4.30956</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2699,39 +2691,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x135ca5b241b0d1e484c97d7c26d71e9d58e6dd971b22360ae9e62df23118ee6b</t>
+          <t>0x2327ae8911b0ecc308e6d44fdd634a294df35dd220e34dae08432da5c5591ea5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.4425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2754,7 +2738,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2784,7 +2768,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786500974</t>
+          <t>1786504569</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2794,7 +2778,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>2.259887</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,12 +2795,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xd0e485c8a54ff92288008fc7ef998bfee28e3c9deabfed91f9266b54b7325639</t>
+          <t>0x96b610f32d9795f8cbb60a70db759bf5c6e8e8bda2b4112f2f4f89d76f146110</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2826,22 +2810,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.5312</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2866,7 +2850,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2896,7 +2880,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786500803</t>
+          <t>1786504435</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2906,7 +2890,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>4.724706</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2923,39 +2907,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x32f75f1a679cbf6e5a754001684967d29f8331ea42c38c104d263619cd26bc14</t>
+          <t>0x3e38be9d0b6d0fa3d03d49d262b9e0803a053310887577ce87e3581fea82ac7d</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>252.25081</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.4775</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -2978,7 +2954,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -3008,7 +2984,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786500801</t>
+          <t>1786504149</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3018,7 +2994,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>528.273948</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3035,39 +3011,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xa4d6707462e7e71482a034711a024006ce64ad33f684e3ffc8aa48e105b8ad86</t>
+          <t>0x4aff54745ee1df9c39e5ceebddd57e339319f03a3082765f5bea3471c3a2fc6f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xceeDe2b5168e0CBeCe1a33e07B384deDB5ea627A</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>690</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -3090,7 +3058,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3120,7 +3088,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786500799</t>
+          <t>1786503841</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3130,7 +3098,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>1550.561798</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3147,12 +3115,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x3efe4e02ea3d9bfa26256cae2117b7deedc84fd159b4045c452040d9b1f2d7c5</t>
+          <t>0xd780d195ce364dd621ce45379699b2c7994680570e51d0eca2c1ed1143572b62</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3162,7 +3130,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1335.26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3232,7 +3200,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786500797</t>
+          <t>1786501059</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3242,7 +3210,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>2400.467416</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3259,12 +3227,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xbc8939d03f5d2c19550a7b112bffcf5adc6d07378d6ceb670253bc89f48240b6</t>
+          <t>0x552df581fa9ee8db3d9033f3b2aae0d7a8a7e68bee7632a0f109eb9c8b3b8551</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3274,7 +3242,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>187.21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3344,7 +3312,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786500775</t>
+          <t>1786500980</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3354,7 +3322,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>336.557303</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3371,7 +3339,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x9aab0146566e1cf2d904cec61e5fc8853c9b003f5b9a0f3c4e69d5d5b5c484ed</t>
+          <t>0x135ca5b241b0d1e484c97d7c26d71e9d58e6dd971b22360ae9e62df23118ee6b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3386,7 +3354,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>63.35999</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3456,7 +3424,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786500773</t>
+          <t>1786500974</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3466,7 +3434,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>113.9056</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3483,7 +3451,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xf93ca08ba4c183f19691ac949364bf8e7941471d36502742e2371e46518e091f</t>
+          <t>0xd0e485c8a54ff92288008fc7ef998bfee28e3c9deabfed91f9266b54b7325639</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3568,7 +3536,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786500761</t>
+          <t>1786500803</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3595,12 +3563,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x81f5973a3f28d7aaeefe7911ffccf1e98af44fcaa930aeac34875dd38df71bc9</t>
+          <t>0x32f75f1a679cbf6e5a754001684967d29f8331ea42c38c104d263619cd26bc14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3610,7 +3578,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26.36</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3680,7 +3648,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786500760</t>
+          <t>1786500801</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3690,7 +3658,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>47.388764</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3707,7 +3675,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x66eeaf3004065d2e62328224d064e8196d58379f132fedbd741c76858295a7f7</t>
+          <t>0xa4d6707462e7e71482a034711a024006ce64ad33f684e3ffc8aa48e105b8ad86</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3792,7 +3760,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786500757</t>
+          <t>1786500799</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3819,12 +3787,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xbad5215a4edd54d38386bd1e5448631e76e90dbee3e4bf3557e8e2c043083418</t>
+          <t>0x3efe4e02ea3d9bfa26256cae2117b7deedc84fd159b4045c452040d9b1f2d7c5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3834,7 +3802,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>104.21999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3904,7 +3872,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786500752</t>
+          <t>1786500797</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3914,7 +3882,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>187.36178</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3931,7 +3899,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xdd309ef6c0dc57692dec182e5cffcdd0c7f85c99189249002a5ee7c4793563d9</t>
+          <t>0xbc8939d03f5d2c19550a7b112bffcf5adc6d07378d6ceb670253bc89f48240b6</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3946,7 +3914,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>83.09999</t>
+          <t>187.21</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4016,7 +3984,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786500737</t>
+          <t>1786500775</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4026,7 +3994,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>149.39324</t>
+          <t>336.557303</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -4043,7 +4011,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x96136c19e8b4b3c1cd9a022ec3ec1be7af2fc0def6358940a3b219bccf20682d</t>
+          <t>0x9aab0146566e1cf2d904cec61e5fc8853c9b003f5b9a0f3c4e69d5d5b5c484ed</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4058,7 +4026,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>63.35999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4128,7 +4096,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786500736</t>
+          <t>1786500773</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4138,7 +4106,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>84.87191</t>
+          <t>113.9056</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4155,23 +4123,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x7b50006545a4d3976ffc8f0762f94bd9fdff1567a3cf664dd9e79edf834c96bc</t>
+          <t>0xf93ca08ba4c183f19691ac949364bf8e7941471d36502742e2371e46518e091f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>197.75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4179,7 +4151,11 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4232,7 +4208,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786500644</t>
+          <t>1786500761</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4242,7 +4218,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>444.382022</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4259,23 +4235,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xf9e921304b5613d4f5a4aac94cdaeac732d8ea42bec44a92191306c7103df732</t>
+          <t>0x81f5973a3f28d7aaeefe7911ffccf1e98af44fcaa930aeac34875dd38df71bc9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>369.91</t>
+          <t>26.36</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4283,7 +4263,11 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4336,7 +4320,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786500633</t>
+          <t>1786500760</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4346,7 +4330,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>831.258427</t>
+          <t>47.388764</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4363,7 +4347,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xdf4ba60566fd5689393750a08058e1a227b21e0bb2b7a75524dd08921158b328</t>
+          <t>0x66eeaf3004065d2e62328224d064e8196d58379f132fedbd741c76858295a7f7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4448,7 +4432,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786500582</t>
+          <t>1786500757</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4475,12 +4459,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x5e90c46cc93882168350f5e6b83523a3325a59dffb9497b35253b8552791e3ab</t>
+          <t>0xbad5215a4edd54d38386bd1e5448631e76e90dbee3e4bf3557e8e2c043083418</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4490,7 +4474,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>104.21999</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4560,7 +4544,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786500580</t>
+          <t>1786500752</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4570,7 +4554,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>187.36178</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4587,7 +4571,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xa18586bdb3003365505e403bdf79edab1b8478a9e9e230f70c4e76fdf6d003cc</t>
+          <t>0xdd309ef6c0dc57692dec182e5cffcdd0c7f85c99189249002a5ee7c4793563d9</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4602,7 +4586,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>83.09999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4672,7 +4656,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786500551</t>
+          <t>1786500737</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4682,7 +4666,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>89.510112</t>
+          <t>149.39324</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4699,7 +4683,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xcee60a04b8f8d5efba6d52111a13199c73c69fd54b9f9f9ba72592c359f92c6a</t>
+          <t>0x96136c19e8b4b3c1cd9a022ec3ec1be7af2fc0def6358940a3b219bccf20682d</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4714,7 +4698,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>47.21</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4784,7 +4768,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786500550</t>
+          <t>1786500736</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4794,7 +4778,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>49.078652</t>
+          <t>84.87191</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4811,27 +4795,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x0909a65a14fd4ad7dbd184945e4e82c9fdce475552b31ac2ffa79f5cc8d2d2fc</t>
+          <t>0x7b50006545a4d3976ffc8f0762f94bd9fdff1567a3cf664dd9e79edf834c96bc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>197.75</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4839,11 +4819,7 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -4896,7 +4872,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786500544</t>
+          <t>1786500644</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4906,7 +4882,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>444.382022</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4923,27 +4899,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xf47ded4743419e912443bb01778bf84bf92c70cb548340b8471b4e65e69d5d72</t>
+          <t>0xf9e921304b5613d4f5a4aac94cdaeac732d8ea42bec44a92191306c7103df732</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>369.91</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4951,11 +4923,7 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -5008,7 +4976,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786500534</t>
+          <t>1786500633</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -5018,7 +4986,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>51.379775</t>
+          <t>831.258427</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5035,7 +5003,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x944f5df4e4d993386c3114a59ad8704373224aae960b40c8fb5dc958868cd0c9</t>
+          <t>0xdf4ba60566fd5689393750a08058e1a227b21e0bb2b7a75524dd08921158b328</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5120,7 +5088,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786500504</t>
+          <t>1786500582</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5147,7 +5115,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x4ffb70fc7ea797009babeaf3a2360c329a379a328dab0ce16fa709514d4f9cef</t>
+          <t>0x5e90c46cc93882168350f5e6b83523a3325a59dffb9497b35253b8552791e3ab</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5232,7 +5200,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786500503</t>
+          <t>1786500580</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5259,12 +5227,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x5c7eb9a2501c32b896b5a9b685517d32cbfe67726fca300d63b10476842d2c2a</t>
+          <t>0xa18586bdb3003365505e403bdf79edab1b8478a9e9e230f70c4e76fdf6d003cc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5274,7 +5242,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5344,7 +5312,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786500501</t>
+          <t>1786500551</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5354,7 +5322,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>89.510112</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5371,12 +5339,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x95e9e1a3038ffc59cdb49a206e8adcb19179a43073a098619bdd395c0570cb37</t>
+          <t>0xcee60a04b8f8d5efba6d52111a13199c73c69fd54b9f9f9ba72592c359f92c6a</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5386,7 +5354,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5456,7 +5424,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786500499</t>
+          <t>1786500550</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5466,7 +5434,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>49.078652</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5483,7 +5451,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x0d5cd46de2f58ac252c6a0489b2fb8253629014f2f6b91d710ba41e1803b36b8</t>
+          <t>0x0909a65a14fd4ad7dbd184945e4e82c9fdce475552b31ac2ffa79f5cc8d2d2fc</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5568,7 +5536,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786500498</t>
+          <t>1786500544</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5595,12 +5563,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x5294d64dc44b1c637243f3de9a061ba385cc84408b2ea0a98d2ddf6c6718815c</t>
+          <t>0xf47ded4743419e912443bb01778bf84bf92c70cb548340b8471b4e65e69d5d72</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5610,7 +5578,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28.58</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5680,7 +5648,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786500496</t>
+          <t>1786500534</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5690,7 +5658,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>8.988764</t>
+          <t>51.379775</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5707,7 +5675,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xb5ce2ecec5f0be7b0047ce88d13d0c9055b5fca8d9c11bc67e966280f2384598</t>
+          <t>0x944f5df4e4d993386c3114a59ad8704373224aae960b40c8fb5dc958868cd0c9</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5792,7 +5760,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786500494</t>
+          <t>1786500504</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5819,7 +5787,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x7c3b5079c34701a023626323d701dfc0a4e7823959dc0481793b08574dc9dfd1</t>
+          <t>0x4ffb70fc7ea797009babeaf3a2360c329a379a328dab0ce16fa709514d4f9cef</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5904,7 +5872,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786500492</t>
+          <t>1786500503</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5931,7 +5899,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xc25d80f3f8534bd014aa3041b4ded1b98e2b6f01f0f432a007e92f8d97721feb</t>
+          <t>0x5c7eb9a2501c32b896b5a9b685517d32cbfe67726fca300d63b10476842d2c2a</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6016,7 +5984,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786500491</t>
+          <t>1786500501</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -6043,12 +6011,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x4b0fefa802aee78ae049407556ceab6fc43dd1967b5944a825593c40843bea6d</t>
+          <t>0x95e9e1a3038ffc59cdb49a206e8adcb19179a43073a098619bdd395c0570cb37</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6058,7 +6026,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6128,7 +6096,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786500476</t>
+          <t>1786500499</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -6138,7 +6106,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>66.570787</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6155,12 +6123,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x8e07b84ce6844c38bd99c9ded59e55289f96bab45374d6cafd8039a6848c3ae1</t>
+          <t>0x0d5cd46de2f58ac252c6a0489b2fb8253629014f2f6b91d710ba41e1803b36b8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6170,7 +6138,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>132.26</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6240,7 +6208,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786500474</t>
+          <t>1786500498</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6250,7 +6218,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>237.770787</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6267,12 +6235,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x0aea6283317d83074694b78f764d29c7b95d51f4e307b7019541bd6400e1a8b8</t>
+          <t>0x5294d64dc44b1c637243f3de9a061ba385cc84408b2ea0a98d2ddf6c6718815c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6282,7 +6250,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>76.86</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6352,7 +6320,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786500468</t>
+          <t>1786500496</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6362,7 +6330,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>138.175281</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6379,12 +6347,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xdda980bbea51d427848750fa29aa6f27e23db79e2c7c5629a9587f9bde755ba9</t>
+          <t>0xb5ce2ecec5f0be7b0047ce88d13d0c9055b5fca8d9c11bc67e966280f2384598</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6394,7 +6362,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>77.35999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6464,7 +6432,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786500460</t>
+          <t>1786500494</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6474,7 +6442,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>139.074139</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6491,12 +6459,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xe29c36778555e41d28b19553e722e94874412123ccb1bedea115d69ba68e5e12</t>
+          <t>0x7c3b5079c34701a023626323d701dfc0a4e7823959dc0481793b08574dc9dfd1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6506,7 +6474,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>41.10999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6576,7 +6544,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786500458</t>
+          <t>1786500492</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6586,7 +6554,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>73.9056</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6603,12 +6571,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x29146d1a0dbde03d831d263bc99690b03cefcdfa8dc20dedd782669d6c9213f9</t>
+          <t>0xc25d80f3f8534bd014aa3041b4ded1b98e2b6f01f0f432a007e92f8d97721feb</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6618,7 +6586,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>120.74</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6688,7 +6656,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786500456</t>
+          <t>1786500491</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6698,7 +6666,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>217.060674</t>
+          <t>8.988764</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6715,7 +6683,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x7bc5af8f4863cacf664ab30c084a2a43acfbcc9eff568595a2106ce23da17209</t>
+          <t>0x4b0fefa802aee78ae049407556ceab6fc43dd1967b5944a825593c40843bea6d</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6730,7 +6698,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6800,7 +6768,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786500454</t>
+          <t>1786500476</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6810,7 +6778,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>49.222472</t>
+          <t>66.570787</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6827,12 +6795,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x5ae0620d3e7fd0d39c61c92d92dff0f44ffb8e289337ebe156f3686d570026cf</t>
+          <t>0x8e07b84ce6844c38bd99c9ded59e55289f96bab45374d6cafd8039a6848c3ae1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6842,7 +6810,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>114.08</t>
+          <t>132.26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6912,7 +6880,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786500453</t>
+          <t>1786500474</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6922,7 +6890,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>205.08764</t>
+          <t>237.770787</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6939,7 +6907,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xf59e1f15c89fd009ceb1441f549470bd61d335d24c57df7a653f34a3fed23904</t>
+          <t>0x0aea6283317d83074694b78f764d29c7b95d51f4e307b7019541bd6400e1a8b8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6954,7 +6922,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>76.86</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7024,7 +6992,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786500452</t>
+          <t>1786500468</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -7034,7 +7002,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>75.595506</t>
+          <t>138.175281</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -7051,7 +7019,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x7d734049fc9657458d52a381d19fb7d4aff8c4e71148efedd691e610e3a7a0bb</t>
+          <t>0xdda980bbea51d427848750fa29aa6f27e23db79e2c7c5629a9587f9bde755ba9</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7066,7 +7034,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1005.29</t>
+          <t>77.35999</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -7136,7 +7104,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786500451</t>
+          <t>1786500460</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -7146,7 +7114,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1807.262921</t>
+          <t>139.074139</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -7163,12 +7131,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xdac326f5927fbb970e6253d4f41b0dda53f675cb5449d4ce88a3392cdb3f18d2</t>
+          <t>0xe29c36778555e41d28b19553e722e94874412123ccb1bedea115d69ba68e5e12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -7178,22 +7146,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>19.56</t>
+          <t>41.10999</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.3975</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7218,7 +7186,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7248,7 +7216,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786499763</t>
+          <t>1786500458</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7258,7 +7226,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>49.207547</t>
+          <t>73.9056</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7275,36 +7243,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xe4d62db20d7dce5a6d3aba1b5840a8cfadcc44c5e125c97cb74db1289ff05051</t>
+          <t>0x29146d1a0dbde03d831d263bc99690b03cefcdfa8dc20dedd782669d6c9213f9</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>120.74</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.2662</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
@@ -7322,7 +7298,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x79833fc6a3f6648404ca4b99628add02ce86c2c2d0053296c7e23bea43b238d1</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7352,7 +7328,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1786498202</t>
+          <t>1786500456</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7362,7 +7338,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>21.408451</t>
+          <t>217.060674</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7379,12 +7355,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x7dcf5f848d78758aa81a9026f7a2af5c72cc084687859ec7c1750f509bdc420b</t>
+          <t>0x7bc5af8f4863cacf664ab30c084a2a43acfbcc9eff568595a2106ce23da17209</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -7394,39 +7370,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -7434,7 +7410,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7464,7 +7440,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1786496166</t>
+          <t>1786500454</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7474,7 +7450,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>10.511211</t>
+          <t>49.222472</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7491,7 +7467,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x42cfdc40991be588eb224c94dbbda3512b84f29d8a76e0e819f1717e16ea7f3a</t>
+          <t>0x5ae0620d3e7fd0d39c61c92d92dff0f44ffb8e289337ebe156f3686d570026cf</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7506,22 +7482,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>26.34</t>
+          <t>114.08</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.5337</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7546,7 +7522,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7576,7 +7552,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1786496166</t>
+          <t>1786500453</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7586,7 +7562,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>49.348946</t>
+          <t>205.08764</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7603,7 +7579,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xfafaa95fa892b7b96feb25237a96968c1542b373c172067c131656aed4764872</t>
+          <t>0xf59e1f15c89fd009ceb1441f549470bd61d335d24c57df7a653f34a3fed23904</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7611,15 +7587,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>22.08887</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7627,7 +7607,11 @@
           <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -7680,7 +7664,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1786495559</t>
+          <t>1786500452</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7690,7 +7674,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>49.498868</t>
+          <t>75.595506</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7707,7 +7691,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x2e1abfbad55d92ecb1113f9023da45bba5096910055bdcd79fd58fee8ad506ef</t>
+          <t>0x7d734049fc9657458d52a381d19fb7d4aff8c4e71148efedd691e610e3a7a0bb</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7715,23 +7699,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>14.82799</t>
+          <t>1005.29</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -7754,7 +7746,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7784,7 +7776,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1786495559</t>
+          <t>1786500451</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7794,7 +7786,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>33.227989</t>
+          <t>1807.262921</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7811,7 +7803,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xda319e704a52e8ad3239c54f090757c46923aed8a6229dbb1a47a6aafdacc178</t>
+          <t>0xdac326f5927fbb970e6253d4f41b0dda53f675cb5449d4ce88a3392cdb3f18d2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7826,22 +7818,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1.14999</t>
+          <t>19.56</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.3975</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7866,7 +7858,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7896,7 +7888,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1786494130</t>
+          <t>1786499763</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7906,7 +7898,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2.04898</t>
+          <t>49.207547</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7923,54 +7915,46 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xe8544bdaf431d2b9cded859bb44c95e9a4cbb77d283569ab427748adf7c38a82</t>
+          <t>0xe4d62db20d7dce5a6d3aba1b5840a8cfadcc44c5e125c97cb74db1289ff05051</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.2662</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -7978,7 +7962,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x79833fc6a3f6648404ca4b99628add02ce86c2c2d0053296c7e23bea43b238d1</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -8008,7 +7992,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1786494129</t>
+          <t>1786498202</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -8018,7 +8002,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>8.232143</t>
+          <t>21.408451</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -8035,12 +8019,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x9f99840ce6a1d8f4c6f24f53d1e8ba96ef427cfa8f43a387601bdf53f416e3a4</t>
+          <t>0x7dcf5f848d78758aa81a9026f7a2af5c72cc084687859ec7c1750f509bdc420b</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8050,22 +8034,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>27.72</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Paris Saint Germain -0.5</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8090,7 +8074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -8120,7 +8104,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1786494097</t>
+          <t>1786496166</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -8130,7 +8114,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>10.511211</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -8147,12 +8131,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x17444d1a79b59787a6df8c716bc91f6b83490b852e7a42e1da13278178bd0fa3</t>
+          <t>0x42cfdc40991be588eb224c94dbbda3512b84f29d8a76e0e819f1717e16ea7f3a</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8162,39 +8146,39 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>26.34</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.5337</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K71" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -8202,7 +8186,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8232,7 +8216,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1786494077</t>
+          <t>1786496166</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -8242,7 +8226,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>28.986547</t>
+          <t>49.348946</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8259,39 +8243,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xed62cce657564c54cdf4505d1beb541e7bb3559d7e8dafcf5c91e22df2dab644</t>
+          <t>0xfafaa95fa892b7b96feb25237a96968c1542b373c172067c131656aed4764872</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>14.27</t>
+          <t>22.08887</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -8314,7 +8290,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -8344,7 +8320,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1786494054</t>
+          <t>1786495559</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -8354,7 +8330,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>58.54359</t>
+          <t>49.498868</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8371,7 +8347,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x5e9b92a3ee864ed306ae19b1eb8415371da432df1801adf9df4096158c2ada97</t>
+          <t>0x2e1abfbad55d92ecb1113f9023da45bba5096910055bdcd79fd58fee8ad506ef</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8382,17 +8358,17 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>22.15226</t>
+          <t>14.82799</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.4475</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8418,7 +8394,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -8448,7 +8424,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1786491019</t>
+          <t>1786495559</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8458,7 +8434,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>49.502257</t>
+          <t>33.227989</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8475,12 +8451,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x23733dbdf9fa3729981e360673c4b7d7c10ff2531e371c5badad3796d6c9c512</t>
+          <t>0xda319e704a52e8ad3239c54f090757c46923aed8a6229dbb1a47a6aafdacc178</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8490,12 +8466,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>27.55999</t>
+          <t>1.14999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.5575</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8560,7 +8536,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1786490560</t>
+          <t>1786494130</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8570,7 +8546,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>49.43496</t>
+          <t>2.04898</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8587,23 +8563,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x0727088f0a4a30c10d202e7c81d28be4eb0ab98bf21e981e558f2e5179605bac</t>
+          <t>0xe8544bdaf431d2b9cded859bb44c95e9a4cbb77d283569ab427748adf7c38a82</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>15.81921</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.4463</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8611,7 +8591,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -8664,7 +8648,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1786490214</t>
+          <t>1786494129</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8674,7 +8658,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>35.44921</t>
+          <t>8.232143</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8691,7 +8675,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x2e03fcc3f7ecc087552ed1d69a1f8008e36e398bfe42ea205ce282f08f1c1340</t>
+          <t>0x9f99840ce6a1d8f4c6f24f53d1e8ba96ef427cfa8f43a387601bdf53f416e3a4</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8706,39 +8690,39 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>13.87999</t>
+          <t>27.72</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.5562</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -8746,7 +8730,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8776,7 +8760,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1786490114</t>
+          <t>1786494097</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8786,7 +8770,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>24.952791</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8803,12 +8787,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x031e42fbfd08a3c7d769259edbc4291e998075aee0ff949b46b2ff5a320f4fb9</t>
+          <t>0x17444d1a79b59787a6df8c716bc91f6b83490b852e7a42e1da13278178bd0fa3</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8818,22 +8802,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.3062</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8858,7 +8842,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8888,7 +8872,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1786487872</t>
+          <t>1786494077</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8898,7 +8882,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>3.62449</t>
+          <t>28.986547</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8915,12 +8899,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x973ce82e34197c696686774e4b32dc293666e3b1f344b3c042ea8e0bc0baf472</t>
+          <t>0xed62cce657564c54cdf4505d1beb541e7bb3559d7e8dafcf5c91e22df2dab644</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8930,12 +8914,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14.27</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.2463</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -9000,7 +8984,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1786484906</t>
+          <t>1786494054</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -9010,7 +8994,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>12.182741</t>
+          <t>58.54359</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9027,39 +9011,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x4189c1704e3efda1c32f863bee5edac536cbbc1ddc5c7ff92ffcec3f8671f4dd</t>
+          <t>0x5e9b92a3ee864ed306ae19b1eb8415371da432df1801adf9df4096158c2ada97</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22.15226</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.4475</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -9082,7 +9058,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9112,7 +9088,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1786483830</t>
+          <t>1786491019</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -9122,7 +9098,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>9.433962</t>
+          <t>49.502257</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9139,12 +9115,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x86035074a77352f25945be3c07a1ce0a72476812a4d9ee7a5d31accc0005ca8e</t>
+          <t>0x23733dbdf9fa3729981e360673c4b7d7c10ff2531e371c5badad3796d6c9c512</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -9154,22 +9130,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2.14549</t>
+          <t>27.55999</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.5275</t>
+          <t>1.5575</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Paris Saint Germain -0.5</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9194,7 +9170,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -9224,7 +9200,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1786483821</t>
+          <t>1786490560</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -9234,7 +9210,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>4.06728</t>
+          <t>49.43496</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -9251,28 +9227,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x95d1a72bec5f6cbef6a0bee578fc49d11315543f98d64986bc30ab10b98ab235</t>
+          <t>0x0727088f0a4a30c10d202e7c81d28be4eb0ab98bf21e981e558f2e5179605bac</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>15.81921</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.6987</t>
+          <t>1.4463</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -9298,7 +9274,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -9328,7 +9304,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1786481014</t>
+          <t>1786490214</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9338,7 +9314,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>429.338104</t>
+          <t>35.44921</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9355,31 +9331,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x75abf2cc9245d94d8697557465991a972b17d428172f9c86e5103ccf4513ae1d</t>
+          <t>0x2e03fcc3f7ecc087552ed1d69a1f8008e36e398bfe42ea205ce282f08f1c1340</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>280.65999</t>
+          <t>13.87999</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5562</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -9402,7 +9386,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -9432,7 +9416,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1786479821</t>
+          <t>1786490114</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9442,7 +9426,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>400.942843</t>
+          <t>24.952791</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9459,12 +9443,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x7b6931100ecd01485a88a37e39d7604129b6c1b4774ef01d18474422b8022991</t>
+          <t>0x031e42fbfd08a3c7d769259edbc4291e998075aee0ff949b46b2ff5a320f4fb9</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -9474,22 +9458,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>295.34</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.3062</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9514,7 +9498,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -9544,7 +9528,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1786479008</t>
+          <t>1786487872</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9554,7 +9538,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1211.651282</t>
+          <t>3.62449</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9571,23 +9555,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0xfd5730799b860d55deb75e792b32577fe97b21a6872bcdcae76b7d727aa3f5e1</t>
+          <t>0x973ce82e34197c696686774e4b32dc293666e3b1f344b3c042ea8e0bc0baf472</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>15.78675</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1.2463</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9595,7 +9583,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -9618,7 +9610,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9648,7 +9640,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1786478908</t>
+          <t>1786484906</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9658,7 +9650,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>35.475843</t>
+          <t>12.182741</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9675,7 +9667,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0xaa6b20356dec3ef3de3c3740df5cda0bfaf51ac484d1b2f78d6d001ebf63c609</t>
+          <t>0x4189c1704e3efda1c32f863bee5edac536cbbc1ddc5c7ff92ffcec3f8671f4dd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9683,23 +9675,31 @@
           <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>0.00327</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.7675</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1786478826</t>
+          <t>1786483830</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>0.004261</t>
+          <t>9.433962</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9779,12 +9779,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x1ca2c2e3faa5fd0586c76f29023f0ae32e5b7eb91a5e924bff0c79c1fd8e3978</t>
+          <t>0x86035074a77352f25945be3c07a1ce0a72476812a4d9ee7a5d31accc0005ca8e</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -9794,22 +9794,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>2.14549</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.5275</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1786478809</t>
+          <t>1786483821</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>31.220513</t>
+          <t>4.06728</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9891,28 +9891,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xd719c5ae636d9e747b1caa23c9df7ac916d22589ebafce09e6a90f528305ad43</t>
+          <t>0x95d1a72bec5f6cbef6a0bee578fc49d11315543f98d64986bc30ab10b98ab235</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x64f5b1770dC9BeAdAA5c573F52472842f8894c8C</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.6987</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1786478807</t>
+          <t>1786481014</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>39.736842</t>
+          <t>429.338104</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9995,7 +9995,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0x7e152d80b0c185c0abe8c4ca426947b4261d81003670d3822de824587a968e1d</t>
+          <t>0x75abf2cc9245d94d8697557465991a972b17d428172f9c86e5103ccf4513ae1d</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10003,31 +10003,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>280.65999</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.5637</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain -0.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10050,7 +10042,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
+          <t>0x409d8b258d8921e8f4a2c11460cbb794c2d8610abb209e4090e8a8ae8f39d2d7</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -10080,7 +10072,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1786478806</t>
+          <t>1786479821</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -10090,7 +10082,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>49.507761</t>
+          <t>400.942843</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10107,12 +10099,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x762726fa569798e9bb38e6d1d3a6718a3e6b17854ec943996f440407d07d5af1</t>
+          <t>0x7b6931100ecd01485a88a37e39d7604129b6c1b4774ef01d18474422b8022991</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -10122,12 +10114,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>30.51955</t>
+          <t>295.34</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -10137,32 +10129,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -10192,7 +10184,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1786478801</t>
+          <t>1786479008</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -10202,7 +10194,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>148.875854</t>
+          <t>1211.651282</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -10219,27 +10211,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x8e47fef69d97d7a182f242c2cdce1afab730128f4310cd28a6f9c5d37adae0d1</t>
+          <t>0xfd5730799b860d55deb75e792b32577fe97b21a6872bcdcae76b7d727aa3f5e1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>36.47459</t>
+          <t>15.78675</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.245</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -10247,11 +10235,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10274,7 +10258,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10304,7 +10288,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1786478798</t>
+          <t>1786478908</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -10314,7 +10298,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>148.875878</t>
+          <t>35.475843</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10331,23 +10315,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x4b13bf02996be9f8f2f945b0a566bfd6a4a430bd57ac43a76f92d64f15f5498d</t>
+          <t>0xaa6b20356dec3ef3de3c3740df5cda0bfaf51ac484d1b2f78d6d001ebf63c609</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>66.06366</t>
+          <t>0.00327</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.4438</t>
+          <t>1.7675</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -10378,7 +10362,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10408,7 +10392,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1786478774</t>
+          <t>1786478826</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -10418,7 +10402,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>148.875854</t>
+          <t>0.004261</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10435,23 +10419,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0xe9e3237227be288d77eb896c110ca16fd4018525f8bcea0d1e30930f9032da8b</t>
+          <t>0x1ca2c2e3faa5fd0586c76f29023f0ae32e5b7eb91a5e924bff0c79c1fd8e3978</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2.10999</t>
+          <t>7.61</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -10459,7 +10447,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10512,7 +10504,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1786478768</t>
+          <t>1786478809</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -10522,7 +10514,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>2.776303</t>
+          <t>31.220513</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10539,7 +10531,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0x4c9eb0ce8768b1300644ee9d6d756f3477ae0a67da7b2d98350ea8c35a646255</t>
+          <t>0xd719c5ae636d9e747b1caa23c9df7ac916d22589ebafce09e6a90f528305ad43</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10547,19 +10539,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13.35</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1.5613</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -10567,26 +10555,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K93" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -10594,7 +10578,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -10624,7 +10608,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>1786478575</t>
+          <t>1786478807</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10634,7 +10618,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>23.786192</t>
+          <t>39.736842</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -10651,7 +10635,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0x3991dd65a93f5a305e8899432f4bb1612f1b874d3aa09a9a9266778002ba1f22</t>
+          <t>0x7e152d80b0c185c0abe8c4ca426947b4261d81003670d3822de824587a968e1d</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10659,23 +10643,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>280.97998</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.5637</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain -0.5</t>
+        </is>
+      </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10698,7 +10690,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x633e1f4af7bf294be4c13c5c783beb3d10adbea62e87950389cb3cfa326086cb</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10728,7 +10720,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>1786478575</t>
+          <t>1786478806</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10738,7 +10730,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>369.7105</t>
+          <t>49.507761</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -10755,12 +10747,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
+          <t>0x762726fa569798e9bb38e6d1d3a6718a3e6b17854ec943996f440407d07d5af1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10770,12 +10762,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>30.51955</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.205</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10785,7 +10777,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10810,7 +10802,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -10840,7 +10832,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>1786477844</t>
+          <t>1786478801</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10850,7 +10842,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>44.882051</t>
+          <t>148.875854</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10867,23 +10859,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
+          <t>0x8e47fef69d97d7a182f242c2cdce1afab730128f4310cd28a6f9c5d37adae0d1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>36.47459</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.245</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -10891,7 +10887,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>1786477225</t>
+          <t>1786478798</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>6016.713092</t>
+          <t>148.875878</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10971,23 +10971,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
+          <t>0x4b13bf02996be9f8f2f945b0a566bfd6a4a430bd57ac43a76f92d64f15f5498d</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0xa498150823d867380b25175554a275c1c668256e</t>
+          <t>0x0dc32f656f382cB67758F43c4d29A281feE11B76</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>688.37615</t>
+          <t>66.06366</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.4487</t>
+          <t>1.4438</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1786476767</t>
+          <t>1786478774</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1533.98585</t>
+          <t>148.875854</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -11075,27 +11075,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
+          <t>0xe9e3237227be288d77eb896c110ca16fd4018525f8bcea0d1e30930f9032da8b</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>2.10999</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1.2437</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -11103,11 +11099,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -11160,7 +11152,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>1786476263</t>
+          <t>1786478768</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -11170,7 +11162,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>73.723077</t>
+          <t>2.776303</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -11187,12 +11179,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
+          <t>0x4c9eb0ce8768b1300644ee9d6d756f3477ae0a67da7b2d98350ea8c35a646255</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11202,22 +11194,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>13.35</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1.3075</t>
+          <t>1.5613</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11242,7 +11234,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -11272,7 +11264,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>1786473059</t>
+          <t>1786478575</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -11282,7 +11274,7 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>15.447154</t>
+          <t>23.786192</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -11299,28 +11291,28 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
+          <t>0x3991dd65a93f5a305e8899432f4bb1612f1b874d3aa09a9a9266778002ba1f22</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>280.97998</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1.0725</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -11346,7 +11338,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -11376,7 +11368,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>1786466862</t>
+          <t>1786478575</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -11386,7 +11378,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>586.482759</t>
+          <t>369.7105</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -11403,7 +11395,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
+          <t>0xb1f0749faa19666cf4234a512073b6fe905a80f4e19d7462647cfe9ceb57c06d</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11411,23 +11403,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>1.5925</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -11450,7 +11450,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>1786466015</t>
+          <t>1786477844</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>16.675105</t>
+          <t>44.882051</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -11507,39 +11507,31 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
+          <t>0xe75fd64786bddcffb26a2ab8aec8ff02c007fcc64ee16062ab2bed40a67d164f</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x85Da26Dce2e5F76FcFb411d89ceb8fcf11A9CBcD</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>119.23</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -11562,7 +11554,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -11592,7 +11584,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>1786465613</t>
+          <t>1786477225</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11602,7 +11594,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>662.388889</t>
+          <t>6016.713092</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -11619,23 +11611,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
+          <t>0x3c9edc4f5c44c0dbcf413728ce35f4f8c68b50f2abbeb2caa42a72a09516164e</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xa498150823d867380b25175554a275c1c668256e</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>688.37615</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.4487</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -11696,7 +11688,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>1786462484</t>
+          <t>1786476767</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11706,7 +11698,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>24.911111</t>
+          <t>1533.98585</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -11723,12 +11715,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
+          <t>0x951615130443e4362647a81545c8c088c7317365c4ffa9a07467321ade98f125</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11738,12 +11730,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>23.9188</t>
+          <t>17.97</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1.2437</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -11753,32 +11745,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x82142b3963732a3fdd36aa8afa37f80a8be5d40f1cde3d8c81b2a40f833fd442</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -11808,7 +11800,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>1786460921</t>
+          <t>1786476263</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11818,7 +11810,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>111.250233</t>
+          <t>73.723077</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11835,31 +11827,39 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
+          <t>0x14d842428ba2fc42cb9122fcef1e8ea4d521ff5e928fa03d4027a9e9d36cce69</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.3075</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x1eb0162b5ef5cce461102a0a0589d643a0342cf1c36981096646de6b5d6f255c</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>1786459823</t>
+          <t>1786473059</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>3.232323</t>
+          <t>15.447154</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11939,28 +11939,28 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
+          <t>0xacfbb4991bf5c10a0276eaf4ab838401611edc56dc36a00f64cbacc0b4aaf142</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.0725</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x1ff093a0d6aad6ea34f9661babedbc7a361e7167b1f31f3dab05f34988e51f47</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>1786459704</t>
+          <t>1786466862</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>343.089431</t>
+          <t>586.482759</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -12043,28 +12043,28 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
+          <t>0xa4e38c77c1133d8be3d4c471cd270781599d373bbf4f6633ea6c2682fde48a52</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>280.99999</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1.615</t>
+          <t>1.5925</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -12090,7 +12090,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0x67230bcb83f942bc217c5d745ea1712885e0906db6bd151cb38c9c1c8672117b</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>1786459347</t>
+          <t>1786466015</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>456.910553</t>
+          <t>16.675105</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -12147,31 +12147,39 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
+          <t>0x0da0312ac7181e4204b626031b1afcd3e2858ddc869ad4c77e972506b878493f</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>312.25</t>
+          <t>119.23</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>1.4825</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -12194,7 +12202,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -12224,7 +12232,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>1786431942</t>
+          <t>1786465613</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -12234,7 +12242,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>647.150259</t>
+          <t>662.388889</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -12251,27 +12259,23 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
+          <t>0xf05a004202d5172597115d20ed24213b9155c5d6fd7480d1fcb926574d5bb930</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>6.00999</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -12279,26 +12283,22 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>1786424623</t>
+          <t>1786462484</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>10.977151</t>
+          <t>24.911111</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -12363,31 +12363,39 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
+          <t>0x9cd0218c04dbf9f8af03b16eef0d1cb40183eedfc941b885be7072ccb0f6a775</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>0xe6a674A10b8bA44d086Cf85791B188209a1F6e2c</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23.9188</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.215</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -12410,7 +12418,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -12440,7 +12448,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>1786421953</t>
+          <t>1786460921</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -12450,7 +12458,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>2.040816</t>
+          <t>111.250233</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -12467,28 +12475,28 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
+          <t>0x315b979409334c6c5a235b8d158f0209e5839bd2f05831b53a9a292c608ee337</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -12514,7 +12522,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -12544,7 +12552,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>1786421917</t>
+          <t>1786459823</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -12554,7 +12562,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>138.77551</t>
+          <t>3.232323</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12571,28 +12579,28 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
+          <t>0x44ab0a6adaab9b2b3e75e30bce10bd9f61fcccddc98d090614d9f0cfb8d3e00d</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>211</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -12618,7 +12626,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -12648,7 +12656,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1786421886</t>
+          <t>1786459704</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -12658,7 +12666,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>18.414322</t>
+          <t>343.089431</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -12675,28 +12683,28 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
+          <t>0xcdcdc100ea2811013be002432e70309f4738884853ece5cc8cd335e1b4ab4d0b</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>216.99999</t>
+          <t>280.99999</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>1.4888</t>
+          <t>1.615</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -12722,7 +12730,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -12752,7 +12760,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>1786409895</t>
+          <t>1786459347</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -12762,7 +12770,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>443.989749</t>
+          <t>456.910553</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -12779,39 +12787,31 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
+          <t>0x391ce88d76018af43c090050bc3937faecb44a3bb6876c2eb020f0d4a40fecb6</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>13.13154</t>
+          <t>312.25</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.4825</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Over 5.0</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -12834,7 +12834,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>1786390904</t>
+          <t>1786431942</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>202.023692</t>
+          <t>647.150259</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -12891,12 +12891,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
+          <t>0x62018a330ac2dc1528134a0e9913f5615e54c162ca453b2e278133061bd850c5</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -12906,22 +12906,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>11.30985</t>
+          <t>6.00999</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Over 5.0</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>1786390902</t>
+          <t>1786424623</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>173.997692</t>
+          <t>10.977151</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -13003,54 +13003,46 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
+          <t>0x0116fe81833bb6a4ed2dbacecc0bf888c42afc5f3f40bf376cb5bbc37cb8d843</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>12.49</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1.5475</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
       <c r="K116" t="inlineStr">
         <is>
           <t>Aston Villa</t>
@@ -13058,7 +13050,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -13088,7 +13080,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>1786371203</t>
+          <t>1786421953</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -13098,7 +13090,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>22.812785</t>
+          <t>2.040816</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -13115,62 +13107,54 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
+          <t>0x8cc01473b0041a94127de7aaaa3c878a17f610392cc876d414055d273a76d3ab</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1.2163</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -13200,7 +13184,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>1786334647</t>
+          <t>1786421917</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -13210,7 +13194,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>13.872832</t>
+          <t>138.77551</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -13227,28 +13211,28 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
+          <t>0x5aa13b0d414124958cbfe600c479d7f26d1e6a5f24ed35b4d6a600eb47503f89</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -13274,7 +13258,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -13304,7 +13288,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>1786316612</t>
+          <t>1786421886</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -13314,7 +13298,7 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>18.414322</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -13331,28 +13315,28 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
+          <t>0xd637b84dae82a7f4481771e1d20283f17db1805dd930164e9bb8dbed3a2b9b48</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0xDF62cAdd15F2cdB9b77E33884C759EE1cC7E6B6F</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>216.99999</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4888</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -13378,7 +13362,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -13408,7 +13392,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>1786316590</t>
+          <t>1786409895</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -13418,7 +13402,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>320.0</t>
+          <t>443.989749</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -13435,31 +13419,39 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
+          <t>0x0ab7816a5b3bdeaa0ba243255d84fb7f5cc3010de74a12da7f4d57039736f910</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>331.57222</t>
+          <t>13.13154</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1.7988</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr"/>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -13482,7 +13474,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -13512,7 +13504,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>1786316229</t>
+          <t>1786390904</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -13522,7 +13514,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>415.11389</t>
+          <t>202.023692</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -13539,31 +13531,39 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+          <t>0x3aecbb07f8e0603691063857af897a5688fe1c580e893e34227756577b554840</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20.70997</t>
+          <t>11.30985</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1.7963</t>
+          <t>1.065</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr"/>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Over 5.0</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -13586,7 +13586,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+          <t>0x05de8cf718f651bf384fc504b594eb03c576258ba7c4caaac4f5ff50201b6be3</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>1786316213</t>
+          <t>1786390902</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>26.009381</t>
+          <t>173.997692</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -13643,12 +13643,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+          <t>0xc97d6568011afd75563e28f1a8282ebccaf6f6273338bd7d8803734afe501645</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -13658,22 +13658,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>12.49</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1.3613</t>
+          <t>1.5475</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Over 3.0</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+          <t>0xd90089ceb0c9854c3d68a3f09fc4fa855b3a26537e60e3a02b69256aaacd29db</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>1786310047</t>
+          <t>1786371203</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>206.726644</t>
+          <t>22.812785</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -13755,12 +13755,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+          <t>0xaf9559a19ef2d1861cd2330ba21b5fd736cd393bd5191bca5483f2fc312d54a0</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+          <t>0x0C2DA7fC8702784d6f75c78Da25460783A6709a0</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -13770,22 +13770,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>65.17485</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1.745</t>
+          <t>1.2163</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Over 1.5</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>1786309443</t>
+          <t>1786334647</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>87.48302</t>
+          <t>13.872832</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -13867,39 +13867,31 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+          <t>0x849efb290909a4a2724fa2fa8a31f1df72258e9472be51c9ba51d2240af02322</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>128</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1.1575</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Under/Over (4)</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Over 4.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
@@ -13922,7 +13914,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -13952,7 +13944,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>1786294983</t>
+          <t>1786316612</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -13962,7 +13954,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>249.015873</t>
+          <t>160.0</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -13979,28 +13971,28 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+          <t>0x2b0477ef51d712b04d8ef50487a04f3c3c81ca210cfe2c567ba0f14a62c50675</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>105.38217</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1.2812</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>UEFA Super Cup</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -14026,7 +14018,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -14056,7 +14048,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786316590</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -14066,7 +14058,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>374.69216</t>
+          <t>320.0</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -14083,27 +14075,23 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+          <t>0xe304d63b730df7947810a5d651289683a05fbd1b8bc83a59cf6e118f7145ff29</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>331.57222</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1.2112</t>
+          <t>1.7988</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -14111,31 +14099,27 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>UEFA Super Cup</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain vs Aston Villa</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Aston Villa</t>
-        </is>
-      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
@@ -14168,7 +14152,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>1786294922</t>
+          <t>1786316229</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -14178,7 +14162,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>341.443787</t>
+          <t>415.11389</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -14195,110 +14179,766 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>0xb37f867e7b09912283071b63d9f0d8dac6471b774c39329e6933acee2f2d4b67</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>20.70997</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1.7963</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>1786316213</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>26.009381</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>0x85dd5b21bc7c1918df3fb950031e49fc0d13fd6e40115f33583a8beab3642acf</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>74.68</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1.3613</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>0x1680a9183d7746c5c4672e850418adf866cefd179c8c9fa8a47ddd9aae14f195</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>1786310047</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>206.726644</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>0xf090a9e8174708f430ff88479074f453c3c72df4065b04abe9083b733a2de742</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>0xE531A1CE55b94E311cC1629a6D68cAcf4F74d044</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>65.17485</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1.745</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Over 1.5</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>0xf1a8eb36f90ceb169cf77914181a6a20df69437e3abbd370109196ebd13c7edb</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>1786309443</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>87.48302</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>0x98179b3dacaa2fd7ee4e1333c1e7254db907c541dd260df7fb7497696b21d6f3</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>39.22</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1.1575</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Under/Over (4)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Over 4.0</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>0xcad766c3bece5254ba9d1a2b8cfdb650e513e674480798bb8979b1e953d44175</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>1786294983</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>249.015873</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>0xf97a74664dd0407e7e5528292e63812f04a796ef7088678563661be1ae37038a</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>105.38217</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1.2812</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>0xe606a9a450716acc469c52d4cd4cc88af08c2e17027af860e1d62789a6948773</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>374.69216</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>0x74d74e84545efa9c898ad15f279d372ae4dcbbf0b95dd8b1d0652f6f472bd4c2</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>72.13</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1.2112</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>UEFA Super Cup</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Paris Saint Germain</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>0x7d79a11368f71901641550937f2120d0c09dccfc84328fabe81c1eb7847ce4b5</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>L19066036</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>1786294922</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>1786561200</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>341.443787</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>0x3694b34366b9210385b305bea639feafe31d2c1f0ae196fbd04597fed8e17499</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>0x2B0D772143059220738CEC4818Ff2a1a499c48fD</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
         <is>
           <t>1.5463</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>Over 2.5</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>UEFA Super Cup</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I133" t="inlineStr">
         <is>
           <t>Paris Saint Germain vs Aston Villa</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="J133" t="inlineStr">
         <is>
           <t>Paris Saint Germain</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="K133" t="inlineStr">
         <is>
           <t>Aston Villa</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t>0x40d2c11bb90148bb1491fd1a5f8f94c6aaefad0b17bf95ff4a50b41a9a0b9b2f</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t>L19066036</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr">
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr">
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
         <is>
           <t>1786234530</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
+      <c r="S133" t="inlineStr">
         <is>
           <t>1786561200</t>
         </is>
       </c>
-      <c r="T127" t="inlineStr">
+      <c r="T133" t="inlineStr">
         <is>
           <t>1.830664</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="U133" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V127" t="inlineStr">
+      <c r="V133" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
